--- a/base_despesas/2026/despesas_202608.xlsx
+++ b/base_despesas/2026/despesas_202608.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>143525.85</v>
+        <v>172231.02</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4204356.21</v>
+        <v>4424061.02</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1792,10 +1792,10 @@
         <v>19021569.48</v>
       </c>
       <c r="S10" t="n">
-        <v>8772157.99</v>
+        <v>8779487.99</v>
       </c>
       <c r="T10" t="n">
-        <v>9686674.050000001</v>
+        <v>9694004.050000001</v>
       </c>
       <c r="U10" t="n">
         <v>11640215.84</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -4571,16 +4571,16 @@
         </is>
       </c>
       <c r="L30" t="n">
+        <v>1105099.62</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
         <v>982211.52</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>982019.1899999999</v>
       </c>
       <c r="P30" t="n">
         <v>614271.01</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2243756</v>
+        <v>2692507.2</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>8260488.78</v>
+        <v>8293797.92</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -4860,7 +4860,7 @@
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>8104293.27</v>
+        <v>8104580.11</v>
       </c>
       <c r="P32" t="n">
         <v>5620655.33</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1631597.99</v>
+        <v>1636075.63</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>8828.879999999999</v>
+        <v>9985.280000000001</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -6671,7 +6671,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2499309.9</v>
+        <v>2508809.9</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -7651,7 +7651,7 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>110894.5</v>
+        <v>133073.4</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -11309,7 +11309,7 @@
         <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>439634</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -11318,7 +11318,7 @@
         <v>0</v>
       </c>
       <c r="U78" t="n">
-        <v>0</v>
+        <v>439634</v>
       </c>
       <c r="V78" t="n">
         <v>0</v>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -12411,7 +12411,7 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>861800</v>
+        <v>993550</v>
       </c>
       <c r="M86" t="n">
         <v>0</v>
@@ -12432,10 +12432,10 @@
         <v>1800000</v>
       </c>
       <c r="S86" t="n">
-        <v>878850</v>
+        <v>1010600</v>
       </c>
       <c r="T86" t="n">
-        <v>878850</v>
+        <v>1010600</v>
       </c>
       <c r="U86" t="n">
         <v>1800000</v>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -14091,7 +14091,7 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>235859.54</v>
+        <v>245768.58</v>
       </c>
       <c r="M98" t="n">
         <v>0</v>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -15211,7 +15211,7 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>32631.35</v>
+        <v>39157.62</v>
       </c>
       <c r="M106" t="n">
         <v>0</v>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>200000</v>
+        <v>280000</v>
       </c>
       <c r="M129" t="n">
         <v>0</v>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -18571,7 +18571,7 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="M130" t="n">
         <v>0</v>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -20811,7 +20811,7 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>1234062.31</v>
+        <v>1279362.31</v>
       </c>
       <c r="M146" t="n">
         <v>0</v>
@@ -20820,7 +20820,7 @@
         <v>0</v>
       </c>
       <c r="O146" t="n">
-        <v>973635.6899999999</v>
+        <v>979135.6899999999</v>
       </c>
       <c r="P146" t="n">
         <v>15454293.91</v>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -21091,7 +21091,7 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>32631.35</v>
+        <v>39157.62</v>
       </c>
       <c r="M148" t="n">
         <v>0</v>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -21371,7 +21371,7 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>143525.85</v>
+        <v>172231.02</v>
       </c>
       <c r="M150" t="n">
         <v>0</v>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -22491,7 +22491,7 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>1533228.18</v>
+        <v>1554642.66</v>
       </c>
       <c r="M158" t="n">
         <v>0</v>
@@ -22500,7 +22500,7 @@
         <v>211572</v>
       </c>
       <c r="O158" t="n">
-        <v>1385977.67</v>
+        <v>1499977.67</v>
       </c>
       <c r="P158" t="n">
         <v>2681423.67</v>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -24889,7 +24889,7 @@
         <v>0</v>
       </c>
       <c r="R175" t="n">
-        <v>350000</v>
+        <v>452872.05</v>
       </c>
       <c r="S175" t="n">
         <v>350000</v>
@@ -24898,7 +24898,7 @@
         <v>350000</v>
       </c>
       <c r="U175" t="n">
-        <v>350000</v>
+        <v>452872.05</v>
       </c>
       <c r="V175" t="n">
         <v>0</v>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -25151,7 +25151,7 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>6321200</v>
+        <v>6290400</v>
       </c>
       <c r="M177" t="n">
         <v>0</v>
@@ -25160,7 +25160,7 @@
         <v>371000</v>
       </c>
       <c r="O177" t="n">
-        <v>5494400</v>
+        <v>6290400</v>
       </c>
       <c r="P177" t="n">
         <v>0</v>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -25711,7 +25711,7 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>649805.4300000001</v>
+        <v>744555.9399999999</v>
       </c>
       <c r="M181" t="n">
         <v>0</v>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -25851,7 +25851,7 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>1465931.48</v>
+        <v>1520548.09</v>
       </c>
       <c r="M182" t="n">
         <v>0</v>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -26131,7 +26131,7 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>11807.1</v>
+        <v>13774.95</v>
       </c>
       <c r="M184" t="n">
         <v>0</v>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -27832,10 +27832,10 @@
         <v>43800</v>
       </c>
       <c r="S196" t="n">
-        <v>18500</v>
+        <v>31800</v>
       </c>
       <c r="T196" t="n">
-        <v>19100</v>
+        <v>32400</v>
       </c>
       <c r="U196" t="n">
         <v>32400</v>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -29351,7 +29351,7 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>118054416.06</v>
+        <v>118161204.58</v>
       </c>
       <c r="M207" t="n">
         <v>0</v>
@@ -29372,10 +29372,10 @@
         <v>214390827.19</v>
       </c>
       <c r="S207" t="n">
-        <v>145404055.55</v>
+        <v>147596374.05</v>
       </c>
       <c r="T207" t="n">
-        <v>151071431.79</v>
+        <v>153263750.29</v>
       </c>
       <c r="U207" t="n">
         <v>164582306.15</v>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -29911,7 +29911,7 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>47531025.9</v>
+        <v>47621025.9</v>
       </c>
       <c r="M211" t="n">
         <v>0</v>
@@ -29923,16 +29923,16 @@
         <v>47172833.45</v>
       </c>
       <c r="P211" t="n">
-        <v>49898263.91</v>
+        <v>50438263.91</v>
       </c>
       <c r="Q211" t="n">
         <v>0</v>
       </c>
       <c r="R211" t="n">
-        <v>129341289.91</v>
+        <v>129881289.91</v>
       </c>
       <c r="S211" t="n">
-        <v>79232487.98999999</v>
+        <v>78962487.98999999</v>
       </c>
       <c r="T211" t="n">
         <v>99116487.98999999</v>
@@ -29941,7 +29941,7 @@
         <v>79443026</v>
       </c>
       <c r="V211" t="n">
-        <v>19884000</v>
+        <v>20154000</v>
       </c>
       <c r="W211" t="n">
         <v>79443026</v>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>07/08/2026 17:32:12</t>
+          <t>08/08/2026 06:57:15</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202608.xlsx
+++ b/base_despesas/2026/despesas_202608.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
         <v>334134</v>
       </c>
       <c r="O7" t="n">
-        <v>139802.25</v>
+        <v>152052.25</v>
       </c>
       <c r="P7" t="n">
         <v>308127.99</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3999063.67</v>
+        <v>4008203.67</v>
       </c>
       <c r="P10" t="n">
         <v>7381353.64</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -6400,7 +6400,7 @@
         <v>131526</v>
       </c>
       <c r="O43" t="n">
-        <v>7181.68</v>
+        <v>8172.88</v>
       </c>
       <c r="P43" t="n">
         <v>67000</v>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -29360,7 +29360,7 @@
         <v>0</v>
       </c>
       <c r="O207" t="n">
-        <v>117370645.55</v>
+        <v>117374145.55</v>
       </c>
       <c r="P207" t="n">
         <v>49808521.04</v>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -29920,7 +29920,7 @@
         <v>0</v>
       </c>
       <c r="O211" t="n">
-        <v>47172833.45</v>
+        <v>47261773.84</v>
       </c>
       <c r="P211" t="n">
         <v>50438263.91</v>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>08/08/2026 06:57:15</t>
+          <t>09/08/2026 06:55:36</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202608.xlsx
+++ b/base_despesas/2026/despesas_202608.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>09/08/2026 06:55:36</t>
+          <t>10/08/2026 07:34:19</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202608.xlsx
+++ b/base_despesas/2026/despesas_202608.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ218"/>
+  <dimension ref="A1:AJ219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>50193.66</v>
+        <v>84393.66</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -958,7 +958,7 @@
         <v>93692.34</v>
       </c>
       <c r="U4" t="n">
-        <v>127892.34</v>
+        <v>93692.34</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>140083.07</v>
+        <v>145749.76</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -4571,7 +4571,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1105099.62</v>
+        <v>1122562.34</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -4592,10 +4592,10 @@
         <v>2456007.01</v>
       </c>
       <c r="S30" t="n">
-        <v>1686622.16</v>
+        <v>1718528.16</v>
       </c>
       <c r="T30" t="n">
-        <v>1843212.94</v>
+        <v>1875118.94</v>
       </c>
       <c r="U30" t="n">
         <v>1841736</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>8293797.92</v>
+        <v>8307446.77</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -5420,7 +5420,7 @@
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>1631597.99</v>
+        <v>1636075.63</v>
       </c>
       <c r="P36" t="n">
         <v>2931914.44</v>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -6671,7 +6671,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2508809.9</v>
+        <v>2510025.21</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -6683,7 +6683,7 @@
         <v>2447815.85</v>
       </c>
       <c r="P45" t="n">
-        <v>16614500.14</v>
+        <v>16620776.87</v>
       </c>
       <c r="Q45" t="n">
         <v>1186346</v>
@@ -6692,16 +6692,16 @@
         <v>31073365.83</v>
       </c>
       <c r="S45" t="n">
-        <v>5308668.53</v>
+        <v>5302391.8</v>
       </c>
       <c r="T45" t="n">
         <v>5735668.95</v>
       </c>
       <c r="U45" t="n">
-        <v>14458865.69</v>
+        <v>14452588.96</v>
       </c>
       <c r="V45" t="n">
-        <v>427000.42</v>
+        <v>433277.15</v>
       </c>
       <c r="W45" t="n">
         <v>14470561.05</v>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -19411,7 +19411,7 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>6276033.41</v>
+        <v>6282898.35</v>
       </c>
       <c r="M136" t="n">
         <v>0</v>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -20811,7 +20811,7 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>1279362.31</v>
+        <v>1282362.31</v>
       </c>
       <c r="M146" t="n">
         <v>0</v>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -22223,7 +22223,7 @@
         <v>46435.29</v>
       </c>
       <c r="P156" t="n">
-        <v>605695.8199999999</v>
+        <v>649248.8199999999</v>
       </c>
       <c r="Q156" t="n">
         <v>8077</v>
@@ -22238,7 +22238,7 @@
         <v>175845.16</v>
       </c>
       <c r="U156" t="n">
-        <v>413183.32</v>
+        <v>369630.32</v>
       </c>
       <c r="V156" t="n">
         <v>0</v>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -23891,7 +23891,7 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>0</v>
+        <v>138463.91</v>
       </c>
       <c r="M168" t="n">
         <v>0</v>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -24307,20 +24307,20 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>7048</t>
+          <t>7047</t>
         </is>
       </c>
       <c r="L171" t="n">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="M171" t="n">
         <v>0</v>
       </c>
       <c r="N171" t="n">
-        <v>578000</v>
+        <v>0</v>
       </c>
       <c r="O171" t="n">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="P171" t="n">
         <v>0</v>
@@ -24329,22 +24329,22 @@
         <v>0</v>
       </c>
       <c r="R171" t="n">
-        <v>578000</v>
+        <v>0</v>
       </c>
       <c r="S171" t="n">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="T171" t="n">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="U171" t="n">
-        <v>578000</v>
+        <v>0</v>
       </c>
       <c r="V171" t="n">
         <v>0</v>
       </c>
       <c r="W171" t="n">
-        <v>578000</v>
+        <v>0</v>
       </c>
       <c r="X171" t="n">
         <v>0</v>
@@ -24356,7 +24356,7 @@
         <v>0</v>
       </c>
       <c r="AA171" t="n">
-        <v>578000</v>
+        <v>0</v>
       </c>
       <c r="AB171" t="n">
         <v>5</v>
@@ -24384,17 +24384,17 @@
       </c>
       <c r="AH171" t="inlineStr">
         <is>
-          <t>Emendas Parlamentares - Senival Moura</t>
+          <t>Emendas Parlamentares - Silvia Ferraro</t>
         </is>
       </c>
       <c r="AI171" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.4329.33503900.00.1.500.7048</t>
+          <t>34.10.14.422.4025.4329.33503900.00.1.500.7047</t>
         </is>
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -24447,20 +24447,20 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>7050</t>
+          <t>7048</t>
         </is>
       </c>
       <c r="L172" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="M172" t="n">
         <v>0</v>
       </c>
       <c r="N172" t="n">
-        <v>125000</v>
+        <v>578000</v>
       </c>
       <c r="O172" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="P172" t="n">
         <v>0</v>
@@ -24469,22 +24469,22 @@
         <v>0</v>
       </c>
       <c r="R172" t="n">
-        <v>0</v>
+        <v>578000</v>
       </c>
       <c r="S172" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="T172" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="U172" t="n">
-        <v>0</v>
+        <v>578000</v>
       </c>
       <c r="V172" t="n">
         <v>0</v>
       </c>
       <c r="W172" t="n">
-        <v>125000</v>
+        <v>578000</v>
       </c>
       <c r="X172" t="n">
         <v>0</v>
@@ -24496,7 +24496,7 @@
         <v>0</v>
       </c>
       <c r="AA172" t="n">
-        <v>125000</v>
+        <v>578000</v>
       </c>
       <c r="AB172" t="n">
         <v>5</v>
@@ -24524,17 +24524,17 @@
       </c>
       <c r="AH172" t="inlineStr">
         <is>
-          <t>Emendas Parlamentares - Hélio Rodrigues</t>
+          <t>Emendas Parlamentares - Senival Moura</t>
         </is>
       </c>
       <c r="AI172" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.4329.33503900.00.1.500.7050</t>
+          <t>34.10.14.422.4025.4329.33503900.00.1.500.7048</t>
         </is>
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -24587,7 +24587,7 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>7070</t>
+          <t>7050</t>
         </is>
       </c>
       <c r="L173" t="n">
@@ -24597,7 +24597,7 @@
         <v>0</v>
       </c>
       <c r="N173" t="n">
-        <v>261000</v>
+        <v>125000</v>
       </c>
       <c r="O173" t="n">
         <v>0</v>
@@ -24624,7 +24624,7 @@
         <v>0</v>
       </c>
       <c r="W173" t="n">
-        <v>261000</v>
+        <v>125000</v>
       </c>
       <c r="X173" t="n">
         <v>0</v>
@@ -24636,7 +24636,7 @@
         <v>0</v>
       </c>
       <c r="AA173" t="n">
-        <v>261000</v>
+        <v>125000</v>
       </c>
       <c r="AB173" t="n">
         <v>5</v>
@@ -24664,17 +24664,17 @@
       </c>
       <c r="AH173" t="inlineStr">
         <is>
-          <t>Emendas Parlamentares - Ana Carolina Oliveira</t>
+          <t>Emendas Parlamentares - Hélio Rodrigues</t>
         </is>
       </c>
       <c r="AI173" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.4329.33503900.00.1.500.7070</t>
+          <t>34.10.14.422.4025.4329.33503900.00.1.500.7050</t>
         </is>
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -24727,20 +24727,20 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>7076</t>
+          <t>7070</t>
         </is>
       </c>
       <c r="L174" t="n">
-        <v>57000</v>
+        <v>0</v>
       </c>
       <c r="M174" t="n">
         <v>0</v>
       </c>
       <c r="N174" t="n">
-        <v>57000</v>
+        <v>261000</v>
       </c>
       <c r="O174" t="n">
-        <v>57000</v>
+        <v>0</v>
       </c>
       <c r="P174" t="n">
         <v>0</v>
@@ -24749,22 +24749,22 @@
         <v>0</v>
       </c>
       <c r="R174" t="n">
-        <v>57000</v>
+        <v>0</v>
       </c>
       <c r="S174" t="n">
-        <v>57000</v>
+        <v>0</v>
       </c>
       <c r="T174" t="n">
-        <v>57000</v>
+        <v>0</v>
       </c>
       <c r="U174" t="n">
-        <v>57000</v>
+        <v>0</v>
       </c>
       <c r="V174" t="n">
         <v>0</v>
       </c>
       <c r="W174" t="n">
-        <v>57000</v>
+        <v>261000</v>
       </c>
       <c r="X174" t="n">
         <v>0</v>
@@ -24776,7 +24776,7 @@
         <v>0</v>
       </c>
       <c r="AA174" t="n">
-        <v>57000</v>
+        <v>261000</v>
       </c>
       <c r="AB174" t="n">
         <v>5</v>
@@ -24804,17 +24804,17 @@
       </c>
       <c r="AH174" t="inlineStr">
         <is>
-          <t>Emendas Parlamentares - Kenji Ito</t>
+          <t>Emendas Parlamentares - Ana Carolina Oliveira</t>
         </is>
       </c>
       <c r="AI174" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.4329.33503900.00.1.500.7076</t>
+          <t>34.10.14.422.4025.4329.33503900.00.1.500.7070</t>
         </is>
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -24867,20 +24867,20 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>7077</t>
+          <t>7076</t>
         </is>
       </c>
       <c r="L175" t="n">
-        <v>150000</v>
+        <v>57000</v>
       </c>
       <c r="M175" t="n">
         <v>0</v>
       </c>
       <c r="N175" t="n">
-        <v>712872.0600000001</v>
+        <v>57000</v>
       </c>
       <c r="O175" t="n">
-        <v>150000</v>
+        <v>57000</v>
       </c>
       <c r="P175" t="n">
         <v>0</v>
@@ -24889,22 +24889,22 @@
         <v>0</v>
       </c>
       <c r="R175" t="n">
-        <v>452872.05</v>
+        <v>57000</v>
       </c>
       <c r="S175" t="n">
-        <v>350000</v>
+        <v>57000</v>
       </c>
       <c r="T175" t="n">
-        <v>350000</v>
+        <v>57000</v>
       </c>
       <c r="U175" t="n">
-        <v>452872.05</v>
+        <v>57000</v>
       </c>
       <c r="V175" t="n">
         <v>0</v>
       </c>
       <c r="W175" t="n">
-        <v>712872.0600000001</v>
+        <v>57000</v>
       </c>
       <c r="X175" t="n">
         <v>0</v>
@@ -24916,7 +24916,7 @@
         <v>0</v>
       </c>
       <c r="AA175" t="n">
-        <v>712872.0600000001</v>
+        <v>57000</v>
       </c>
       <c r="AB175" t="n">
         <v>5</v>
@@ -24944,17 +24944,17 @@
       </c>
       <c r="AH175" t="inlineStr">
         <is>
-          <t>Emendas Parlamentares - Lucas Pavanato</t>
+          <t>Emendas Parlamentares - Kenji Ito</t>
         </is>
       </c>
       <c r="AI175" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.4329.33503900.00.1.500.7077</t>
+          <t>34.10.14.422.4025.4329.33503900.00.1.500.7076</t>
         </is>
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -25007,20 +25007,20 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>7087</t>
+          <t>7077</t>
         </is>
       </c>
       <c r="L176" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="M176" t="n">
         <v>0</v>
       </c>
       <c r="N176" t="n">
-        <v>318150</v>
+        <v>712872.0600000001</v>
       </c>
       <c r="O176" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="P176" t="n">
         <v>0</v>
@@ -25029,22 +25029,22 @@
         <v>0</v>
       </c>
       <c r="R176" t="n">
-        <v>318150</v>
+        <v>452872.05</v>
       </c>
       <c r="S176" t="n">
-        <v>318150</v>
+        <v>350000</v>
       </c>
       <c r="T176" t="n">
-        <v>318150</v>
+        <v>350000</v>
       </c>
       <c r="U176" t="n">
-        <v>318150</v>
+        <v>452872.05</v>
       </c>
       <c r="V176" t="n">
         <v>0</v>
       </c>
       <c r="W176" t="n">
-        <v>318150</v>
+        <v>712872.0600000001</v>
       </c>
       <c r="X176" t="n">
         <v>0</v>
@@ -25056,7 +25056,7 @@
         <v>0</v>
       </c>
       <c r="AA176" t="n">
-        <v>318150</v>
+        <v>712872.0600000001</v>
       </c>
       <c r="AB176" t="n">
         <v>5</v>
@@ -25084,17 +25084,17 @@
       </c>
       <c r="AH176" t="inlineStr">
         <is>
-          <t>Emendas Parlamentares - Zoe Martínez</t>
+          <t>Emendas Parlamentares - Lucas Pavanato</t>
         </is>
       </c>
       <c r="AI176" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.4329.33503900.00.1.500.7087</t>
+          <t>34.10.14.422.4025.4329.33503900.00.1.500.7077</t>
         </is>
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -25137,7 +25137,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>33904800</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -25147,56 +25147,56 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>7087</t>
         </is>
       </c>
       <c r="L177" t="n">
-        <v>6290400</v>
+        <v>0</v>
       </c>
       <c r="M177" t="n">
         <v>0</v>
       </c>
       <c r="N177" t="n">
-        <v>371000</v>
+        <v>318150</v>
       </c>
       <c r="O177" t="n">
-        <v>6290400</v>
+        <v>0</v>
       </c>
       <c r="P177" t="n">
         <v>0</v>
       </c>
       <c r="Q177" t="n">
-        <v>1421600</v>
+        <v>0</v>
       </c>
       <c r="R177" t="n">
-        <v>9076439.67</v>
+        <v>318150</v>
       </c>
       <c r="S177" t="n">
-        <v>6355600</v>
+        <v>318150</v>
       </c>
       <c r="T177" t="n">
-        <v>7228800</v>
+        <v>318150</v>
       </c>
       <c r="U177" t="n">
-        <v>9076439.67</v>
+        <v>318150</v>
       </c>
       <c r="V177" t="n">
-        <v>873200</v>
+        <v>0</v>
       </c>
       <c r="W177" t="n">
-        <v>9076439.67</v>
+        <v>318150</v>
       </c>
       <c r="X177" t="n">
-        <v>10000000</v>
+        <v>0</v>
       </c>
       <c r="Y177" t="n">
-        <v>1421600</v>
+        <v>0</v>
       </c>
       <c r="Z177" t="n">
-        <v>1294560.33</v>
+        <v>0</v>
       </c>
       <c r="AA177" t="n">
-        <v>9076439.67</v>
+        <v>318150</v>
       </c>
       <c r="AB177" t="n">
         <v>5</v>
@@ -25219,22 +25219,22 @@
       </c>
       <c r="AG177" t="inlineStr">
         <is>
-          <t>Outros Auxílios Financeiros - Pessoas Físicas</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Emendas Parlamentares - Zoe Martínez</t>
         </is>
       </c>
       <c r="AI177" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.4329.33904800.00.1.500.9001</t>
+          <t>34.10.14.422.4025.4329.33503900.00.1.500.7087</t>
         </is>
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -25267,7 +25267,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>6178</t>
+          <t>4329</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -25277,7 +25277,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33904800</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -25291,52 +25291,52 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>24306394.23</v>
+        <v>6290400</v>
       </c>
       <c r="M178" t="n">
         <v>0</v>
       </c>
       <c r="N178" t="n">
-        <v>2800000</v>
+        <v>371000</v>
       </c>
       <c r="O178" t="n">
-        <v>24181560.43</v>
+        <v>6290400</v>
       </c>
       <c r="P178" t="n">
-        <v>1885306.26</v>
+        <v>0</v>
       </c>
       <c r="Q178" t="n">
-        <v>0</v>
+        <v>1421600</v>
       </c>
       <c r="R178" t="n">
-        <v>27111664.26</v>
+        <v>9076439.67</v>
       </c>
       <c r="S178" t="n">
-        <v>25225912.81</v>
+        <v>6355600</v>
       </c>
       <c r="T178" t="n">
-        <v>25892927.01</v>
+        <v>7228800</v>
       </c>
       <c r="U178" t="n">
-        <v>25226358</v>
+        <v>9076439.67</v>
       </c>
       <c r="V178" t="n">
-        <v>667014.2</v>
+        <v>873200</v>
       </c>
       <c r="W178" t="n">
-        <v>25226358</v>
+        <v>9076439.67</v>
       </c>
       <c r="X178" t="n">
-        <v>22426358</v>
+        <v>10000000</v>
       </c>
       <c r="Y178" t="n">
-        <v>0</v>
+        <v>1421600</v>
       </c>
       <c r="Z178" t="n">
-        <v>0</v>
+        <v>1294560.33</v>
       </c>
       <c r="AA178" t="n">
-        <v>25226358</v>
+        <v>9076439.67</v>
       </c>
       <c r="AB178" t="n">
         <v>5</v>
@@ -25349,7 +25349,7 @@
       </c>
       <c r="AE178" t="inlineStr">
         <is>
-          <t>CPM - Equipamentos</t>
+          <t>CPM - Políticas</t>
         </is>
       </c>
       <c r="AF178" t="inlineStr">
@@ -25359,7 +25359,7 @@
       </c>
       <c r="AG178" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Outros Auxílios Financeiros - Pessoas Físicas</t>
         </is>
       </c>
       <c r="AH178" t="inlineStr">
@@ -25369,12 +25369,12 @@
       </c>
       <c r="AI178" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.6178.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4025.4329.33904800.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -25417,7 +25417,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -25431,43 +25431,43 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>82853.60000000001</v>
+        <v>24306394.23</v>
       </c>
       <c r="M179" t="n">
         <v>0</v>
       </c>
       <c r="N179" t="n">
-        <v>52998</v>
+        <v>2800000</v>
       </c>
       <c r="O179" t="n">
-        <v>82853.60000000001</v>
+        <v>24181560.43</v>
       </c>
       <c r="P179" t="n">
-        <v>7647.82</v>
+        <v>1885306.26</v>
       </c>
       <c r="Q179" t="n">
         <v>0</v>
       </c>
       <c r="R179" t="n">
-        <v>228416.15</v>
+        <v>27111664.26</v>
       </c>
       <c r="S179" t="n">
-        <v>160506.12</v>
+        <v>25225912.81</v>
       </c>
       <c r="T179" t="n">
-        <v>162300.12</v>
+        <v>25892927.01</v>
       </c>
       <c r="U179" t="n">
-        <v>220768.33</v>
+        <v>25226358</v>
       </c>
       <c r="V179" t="n">
-        <v>1794</v>
+        <v>667014.2</v>
       </c>
       <c r="W179" t="n">
-        <v>252998</v>
+        <v>25226358</v>
       </c>
       <c r="X179" t="n">
-        <v>200000</v>
+        <v>22426358</v>
       </c>
       <c r="Y179" t="n">
         <v>0</v>
@@ -25476,7 +25476,7 @@
         <v>0</v>
       </c>
       <c r="AA179" t="n">
-        <v>252998</v>
+        <v>25226358</v>
       </c>
       <c r="AB179" t="n">
         <v>5</v>
@@ -25499,7 +25499,7 @@
       </c>
       <c r="AG179" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH179" t="inlineStr">
@@ -25509,12 +25509,12 @@
       </c>
       <c r="AI179" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.6178.33903000.00.1.500.9001</t>
+          <t>34.10.14.422.4025.6178.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -25557,7 +25557,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>33903600</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -25571,43 +25571,43 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>73676.8</v>
+        <v>82853.60000000001</v>
       </c>
       <c r="M180" t="n">
         <v>0</v>
       </c>
       <c r="N180" t="n">
-        <v>0</v>
+        <v>52998</v>
       </c>
       <c r="O180" t="n">
-        <v>73676.8</v>
+        <v>82853.60000000001</v>
       </c>
       <c r="P180" t="n">
-        <v>0</v>
+        <v>7647.82</v>
       </c>
       <c r="Q180" t="n">
         <v>0</v>
       </c>
       <c r="R180" t="n">
-        <v>142934.93</v>
+        <v>228416.15</v>
       </c>
       <c r="S180" t="n">
-        <v>142934.93</v>
+        <v>160506.12</v>
       </c>
       <c r="T180" t="n">
-        <v>142934.93</v>
+        <v>162300.12</v>
       </c>
       <c r="U180" t="n">
-        <v>142934.93</v>
+        <v>220768.33</v>
       </c>
       <c r="V180" t="n">
-        <v>0</v>
+        <v>1794</v>
       </c>
       <c r="W180" t="n">
-        <v>250000</v>
+        <v>252998</v>
       </c>
       <c r="X180" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="Y180" t="n">
         <v>0</v>
@@ -25616,7 +25616,7 @@
         <v>0</v>
       </c>
       <c r="AA180" t="n">
-        <v>250000</v>
+        <v>252998</v>
       </c>
       <c r="AB180" t="n">
         <v>5</v>
@@ -25639,7 +25639,7 @@
       </c>
       <c r="AG180" t="inlineStr">
         <is>
-          <t>Contratação PF</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AH180" t="inlineStr">
@@ -25649,12 +25649,12 @@
       </c>
       <c r="AI180" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.6178.33903600.00.1.500.9001</t>
+          <t>34.10.14.422.4025.6178.33903000.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -25697,7 +25697,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>33903700</t>
+          <t>33903600</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -25711,7 +25711,7 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>744555.9399999999</v>
+        <v>84789.60000000001</v>
       </c>
       <c r="M181" t="n">
         <v>0</v>
@@ -25720,43 +25720,43 @@
         <v>0</v>
       </c>
       <c r="O181" t="n">
-        <v>620095.8199999999</v>
+        <v>73676.8</v>
       </c>
       <c r="P181" t="n">
-        <v>1473088.82</v>
+        <v>0</v>
       </c>
       <c r="Q181" t="n">
         <v>0</v>
       </c>
       <c r="R181" t="n">
-        <v>3975902.75</v>
+        <v>142934.93</v>
       </c>
       <c r="S181" t="n">
-        <v>1333260.32</v>
+        <v>142934.93</v>
       </c>
       <c r="T181" t="n">
-        <v>1400186.16</v>
+        <v>142934.93</v>
       </c>
       <c r="U181" t="n">
-        <v>2502813.93</v>
+        <v>142934.93</v>
       </c>
       <c r="V181" t="n">
-        <v>66925.84</v>
+        <v>0</v>
       </c>
       <c r="W181" t="n">
-        <v>2512525.33</v>
+        <v>250000</v>
       </c>
       <c r="X181" t="n">
-        <v>2537927</v>
+        <v>250000</v>
       </c>
       <c r="Y181" t="n">
         <v>0</v>
       </c>
       <c r="Z181" t="n">
-        <v>25401.67</v>
+        <v>0</v>
       </c>
       <c r="AA181" t="n">
-        <v>2512525.33</v>
+        <v>250000</v>
       </c>
       <c r="AB181" t="n">
         <v>5</v>
@@ -25779,7 +25779,7 @@
       </c>
       <c r="AG181" t="inlineStr">
         <is>
-          <t>Locação de Mão de Obra</t>
+          <t>Contratação PF</t>
         </is>
       </c>
       <c r="AH181" t="inlineStr">
@@ -25789,12 +25789,12 @@
       </c>
       <c r="AI181" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.6178.33903700.00.1.500.9001</t>
+          <t>34.10.14.422.4025.6178.33903600.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -25837,7 +25837,7 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903700</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -25851,7 +25851,7 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>1520548.09</v>
+        <v>744555.9399999999</v>
       </c>
       <c r="M182" t="n">
         <v>0</v>
@@ -25860,43 +25860,43 @@
         <v>0</v>
       </c>
       <c r="O182" t="n">
-        <v>1445805.7</v>
+        <v>620095.8199999999</v>
       </c>
       <c r="P182" t="n">
-        <v>1815228.97</v>
+        <v>1473088.82</v>
       </c>
       <c r="Q182" t="n">
         <v>0</v>
       </c>
       <c r="R182" t="n">
-        <v>5517841.82</v>
+        <v>3975902.75</v>
       </c>
       <c r="S182" t="n">
-        <v>2413857.99</v>
+        <v>1333260.32</v>
       </c>
       <c r="T182" t="n">
-        <v>2507776.98</v>
+        <v>1400186.16</v>
       </c>
       <c r="U182" t="n">
-        <v>3702612.85</v>
+        <v>2502813.93</v>
       </c>
       <c r="V182" t="n">
-        <v>93918.99000000001</v>
+        <v>66925.84</v>
       </c>
       <c r="W182" t="n">
-        <v>3735019</v>
+        <v>2512525.33</v>
       </c>
       <c r="X182" t="n">
-        <v>4806049</v>
+        <v>2537927</v>
       </c>
       <c r="Y182" t="n">
-        <v>65487</v>
+        <v>0</v>
       </c>
       <c r="Z182" t="n">
-        <v>1005543</v>
+        <v>25401.67</v>
       </c>
       <c r="AA182" t="n">
-        <v>3800506</v>
+        <v>2512525.33</v>
       </c>
       <c r="AB182" t="n">
         <v>5</v>
@@ -25919,7 +25919,7 @@
       </c>
       <c r="AG182" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Locação de Mão de Obra</t>
         </is>
       </c>
       <c r="AH182" t="inlineStr">
@@ -25929,12 +25929,12 @@
       </c>
       <c r="AI182" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.6178.33903900.00.1.500.9001</t>
+          <t>34.10.14.422.4025.6178.33903700.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -25987,11 +25987,11 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L183" t="n">
-        <v>368.19</v>
+        <v>1520667.89</v>
       </c>
       <c r="M183" t="n">
         <v>0</v>
@@ -26000,43 +26000,43 @@
         <v>0</v>
       </c>
       <c r="O183" t="n">
-        <v>368.19</v>
+        <v>1445805.7</v>
       </c>
       <c r="P183" t="n">
-        <v>0</v>
+        <v>1825657.74</v>
       </c>
       <c r="Q183" t="n">
         <v>0</v>
       </c>
       <c r="R183" t="n">
-        <v>80100</v>
+        <v>5517841.82</v>
       </c>
       <c r="S183" t="n">
-        <v>73100</v>
+        <v>2403429.22</v>
       </c>
       <c r="T183" t="n">
-        <v>80100</v>
+        <v>2507776.98</v>
       </c>
       <c r="U183" t="n">
-        <v>80100</v>
+        <v>3692184.08</v>
       </c>
       <c r="V183" t="n">
-        <v>7000</v>
+        <v>104347.76</v>
       </c>
       <c r="W183" t="n">
-        <v>139282</v>
+        <v>3735019</v>
       </c>
       <c r="X183" t="n">
-        <v>139282</v>
+        <v>4806049</v>
       </c>
       <c r="Y183" t="n">
-        <v>0</v>
+        <v>65487</v>
       </c>
       <c r="Z183" t="n">
-        <v>0</v>
+        <v>1005543</v>
       </c>
       <c r="AA183" t="n">
-        <v>139282</v>
+        <v>3800506</v>
       </c>
       <c r="AB183" t="n">
         <v>5</v>
@@ -26064,17 +26064,17 @@
       </c>
       <c r="AH183" t="inlineStr">
         <is>
-          <t>Recursos destinados ao pagamento de concessionárias</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI183" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.6178.33903900.00.1.500.9006</t>
+          <t>34.10.14.422.4025.6178.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -26117,7 +26117,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>33904700</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -26127,11 +26127,11 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="L184" t="n">
-        <v>13774.95</v>
+        <v>368.19</v>
       </c>
       <c r="M184" t="n">
         <v>0</v>
@@ -26140,7 +26140,7 @@
         <v>0</v>
       </c>
       <c r="O184" t="n">
-        <v>11807.1</v>
+        <v>368.19</v>
       </c>
       <c r="P184" t="n">
         <v>0</v>
@@ -26149,25 +26149,25 @@
         <v>0</v>
       </c>
       <c r="R184" t="n">
-        <v>19678.5</v>
+        <v>80100</v>
       </c>
       <c r="S184" t="n">
-        <v>19678.5</v>
+        <v>73100</v>
       </c>
       <c r="T184" t="n">
-        <v>19678.5</v>
+        <v>80100</v>
       </c>
       <c r="U184" t="n">
-        <v>19678.5</v>
+        <v>80100</v>
       </c>
       <c r="V184" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="W184" t="n">
-        <v>49000</v>
+        <v>139282</v>
       </c>
       <c r="X184" t="n">
-        <v>49000</v>
+        <v>139282</v>
       </c>
       <c r="Y184" t="n">
         <v>0</v>
@@ -26176,7 +26176,7 @@
         <v>0</v>
       </c>
       <c r="AA184" t="n">
-        <v>49000</v>
+        <v>139282</v>
       </c>
       <c r="AB184" t="n">
         <v>5</v>
@@ -26199,22 +26199,22 @@
       </c>
       <c r="AG184" t="inlineStr">
         <is>
-          <t>Obrigações Tributárias e Contributivas</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH184" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Recursos destinados ao pagamento de concessionárias</t>
         </is>
       </c>
       <c r="AI184" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.6178.33904700.00.1.500.9001</t>
+          <t>34.10.14.422.4025.6178.33903900.00.1.500.9006</t>
         </is>
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -26247,17 +26247,17 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>9027</t>
+          <t>6178</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>CPM</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33904700</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -26271,7 +26271,7 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>0</v>
+        <v>13774.95</v>
       </c>
       <c r="M185" t="n">
         <v>0</v>
@@ -26280,43 +26280,43 @@
         <v>0</v>
       </c>
       <c r="O185" t="n">
-        <v>0</v>
+        <v>13774.95</v>
       </c>
       <c r="P185" t="n">
         <v>0</v>
       </c>
       <c r="Q185" t="n">
-        <v>329000</v>
+        <v>0</v>
       </c>
       <c r="R185" t="n">
-        <v>0</v>
+        <v>19678.5</v>
       </c>
       <c r="S185" t="n">
-        <v>0</v>
+        <v>19678.5</v>
       </c>
       <c r="T185" t="n">
-        <v>0</v>
+        <v>19678.5</v>
       </c>
       <c r="U185" t="n">
-        <v>0</v>
+        <v>19678.5</v>
       </c>
       <c r="V185" t="n">
         <v>0</v>
       </c>
       <c r="W185" t="n">
-        <v>0</v>
+        <v>49000</v>
       </c>
       <c r="X185" t="n">
-        <v>110000</v>
+        <v>49000</v>
       </c>
       <c r="Y185" t="n">
-        <v>330000</v>
+        <v>0</v>
       </c>
       <c r="Z185" t="n">
-        <v>109000</v>
+        <v>0</v>
       </c>
       <c r="AA185" t="n">
-        <v>1000</v>
+        <v>49000</v>
       </c>
       <c r="AB185" t="n">
         <v>5</v>
@@ -26324,12 +26324,12 @@
       <c r="AC185" t="inlineStr"/>
       <c r="AD185" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>Mulheres</t>
         </is>
       </c>
       <c r="AE185" t="inlineStr">
         <is>
-          <t>E2897 - Realização do projeto "Formação no Enfrentamento à Violência Contra as Mulheres". Organizaçã</t>
+          <t>CPM - Equipamentos</t>
         </is>
       </c>
       <c r="AF185" t="inlineStr">
@@ -26339,7 +26339,7 @@
       </c>
       <c r="AG185" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Obrigações Tributárias e Contributivas</t>
         </is>
       </c>
       <c r="AH185" t="inlineStr">
@@ -26349,12 +26349,12 @@
       </c>
       <c r="AI185" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.9027.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4025.6178.33904700.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -26387,7 +26387,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>9030</t>
+          <t>9027</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -26426,7 +26426,7 @@
         <v>0</v>
       </c>
       <c r="Q186" t="n">
-        <v>300000</v>
+        <v>329000</v>
       </c>
       <c r="R186" t="n">
         <v>0</v>
@@ -26447,16 +26447,16 @@
         <v>0</v>
       </c>
       <c r="X186" t="n">
-        <v>100000</v>
+        <v>110000</v>
       </c>
       <c r="Y186" t="n">
-        <v>300000</v>
+        <v>330000</v>
       </c>
       <c r="Z186" t="n">
-        <v>100000</v>
+        <v>109000</v>
       </c>
       <c r="AA186" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB186" t="n">
         <v>5</v>
@@ -26469,7 +26469,7 @@
       </c>
       <c r="AE186" t="inlineStr">
         <is>
-          <t>E2913 - Realização do Projeto "Formação para todas as Cidadãs Cantantes". Organização: Associação SO</t>
+          <t>E2897 - Realização do projeto "Formação no Enfrentamento à Violência Contra as Mulheres". Organizaçã</t>
         </is>
       </c>
       <c r="AF186" t="inlineStr">
@@ -26489,12 +26489,12 @@
       </c>
       <c r="AI186" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.9030.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4025.9027.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -26527,7 +26527,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>9044</t>
+          <t>9030</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -26566,7 +26566,7 @@
         <v>0</v>
       </c>
       <c r="Q187" t="n">
-        <v>75000</v>
+        <v>300000</v>
       </c>
       <c r="R187" t="n">
         <v>0</v>
@@ -26587,13 +26587,13 @@
         <v>0</v>
       </c>
       <c r="X187" t="n">
-        <v>75000</v>
+        <v>100000</v>
       </c>
       <c r="Y187" t="n">
-        <v>75000</v>
+        <v>300000</v>
       </c>
       <c r="Z187" t="n">
-        <v>75000</v>
+        <v>100000</v>
       </c>
       <c r="AA187" t="n">
         <v>0</v>
@@ -26609,7 +26609,7 @@
       </c>
       <c r="AE187" t="inlineStr">
         <is>
-          <t>E312 - Formação para Grupos em Mulheres em Práticas Artísticas, Educacionais, Esportivas - Arandu</t>
+          <t>E2913 - Realização do Projeto "Formação para todas as Cidadãs Cantantes". Organização: Associação SO</t>
         </is>
       </c>
       <c r="AF187" t="inlineStr">
@@ -26629,12 +26629,12 @@
       </c>
       <c r="AI187" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.9044.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4025.9030.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -26663,16 +26663,16 @@
         <v>422</v>
       </c>
       <c r="F188" t="n">
-        <v>4026</v>
+        <v>4025</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>4327</t>
+          <t>9044</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>CPIR</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -26687,7 +26687,7 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>7026</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L188" t="n">
@@ -26697,7 +26697,7 @@
         <v>0</v>
       </c>
       <c r="N188" t="n">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="O188" t="n">
         <v>0</v>
@@ -26706,7 +26706,7 @@
         <v>0</v>
       </c>
       <c r="Q188" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="R188" t="n">
         <v>0</v>
@@ -26724,19 +26724,19 @@
         <v>0</v>
       </c>
       <c r="W188" t="n">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="X188" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="Y188" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="Z188" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="AA188" t="n">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="AB188" t="n">
         <v>5</v>
@@ -26744,12 +26744,12 @@
       <c r="AC188" t="inlineStr"/>
       <c r="AD188" t="inlineStr">
         <is>
-          <t>Igualdade Racial</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE188" t="inlineStr">
         <is>
-          <t>CPIR - Políticas</t>
+          <t>E312 - Formação para Grupos em Mulheres em Práticas Artísticas, Educacionais, Esportivas - Arandu</t>
         </is>
       </c>
       <c r="AF188" t="inlineStr">
@@ -26764,17 +26764,17 @@
       </c>
       <c r="AH188" t="inlineStr">
         <is>
-          <t>Emendas Parlamentares - Luana Alves</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI188" t="inlineStr">
         <is>
-          <t>34.10.14.422.4026.4327.33503900.00.1.500.7026</t>
+          <t>34.10.14.422.4025.9044.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -26817,7 +26817,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -26827,7 +26827,7 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>7026</t>
         </is>
       </c>
       <c r="L189" t="n">
@@ -26837,7 +26837,7 @@
         <v>0</v>
       </c>
       <c r="N189" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -26864,10 +26864,10 @@
         <v>0</v>
       </c>
       <c r="W189" t="n">
-        <v>11949</v>
+        <v>200000</v>
       </c>
       <c r="X189" t="n">
-        <v>11949</v>
+        <v>0</v>
       </c>
       <c r="Y189" t="n">
         <v>0</v>
@@ -26876,7 +26876,7 @@
         <v>0</v>
       </c>
       <c r="AA189" t="n">
-        <v>11949</v>
+        <v>200000</v>
       </c>
       <c r="AB189" t="n">
         <v>5</v>
@@ -26899,22 +26899,22 @@
       </c>
       <c r="AG189" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH189" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Emendas Parlamentares - Luana Alves</t>
         </is>
       </c>
       <c r="AI189" t="inlineStr">
         <is>
-          <t>34.10.14.422.4026.4327.33903900.00.1.500.9001</t>
+          <t>34.10.14.422.4026.4327.33503900.00.1.500.7026</t>
         </is>
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -26947,7 +26947,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>4334</t>
+          <t>4327</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -26957,7 +26957,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -26971,52 +26971,52 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>7909901.72</v>
+        <v>0</v>
       </c>
       <c r="M190" t="n">
         <v>0</v>
       </c>
       <c r="N190" t="n">
-        <v>2173491.67</v>
+        <v>0</v>
       </c>
       <c r="O190" t="n">
-        <v>7909901.72</v>
+        <v>0</v>
       </c>
       <c r="P190" t="n">
-        <v>1098604.07</v>
+        <v>0</v>
       </c>
       <c r="Q190" t="n">
-        <v>2986219</v>
+        <v>0</v>
       </c>
       <c r="R190" t="n">
-        <v>9727587.74</v>
+        <v>0</v>
       </c>
       <c r="S190" t="n">
-        <v>7909901.72</v>
+        <v>0</v>
       </c>
       <c r="T190" t="n">
-        <v>9008505.779999999</v>
+        <v>0</v>
       </c>
       <c r="U190" t="n">
-        <v>8628983.67</v>
+        <v>0</v>
       </c>
       <c r="V190" t="n">
-        <v>1098604.06</v>
+        <v>0</v>
       </c>
       <c r="W190" t="n">
-        <v>8628983.67</v>
+        <v>11949</v>
       </c>
       <c r="X190" t="n">
-        <v>6455492</v>
+        <v>11949</v>
       </c>
       <c r="Y190" t="n">
-        <v>2986219</v>
+        <v>0</v>
       </c>
       <c r="Z190" t="n">
         <v>0</v>
       </c>
       <c r="AA190" t="n">
-        <v>8628983.67</v>
+        <v>11949</v>
       </c>
       <c r="AB190" t="n">
         <v>5</v>
@@ -27029,7 +27029,7 @@
       </c>
       <c r="AE190" t="inlineStr">
         <is>
-          <t>CPIR - Equipamentos</t>
+          <t>CPIR - Políticas</t>
         </is>
       </c>
       <c r="AF190" t="inlineStr">
@@ -27039,7 +27039,7 @@
       </c>
       <c r="AG190" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH190" t="inlineStr">
@@ -27049,12 +27049,12 @@
       </c>
       <c r="AI190" t="inlineStr">
         <is>
-          <t>34.10.14.422.4026.4334.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4026.4327.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -27097,7 +27097,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>33903100</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -27111,52 +27111,52 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>9864</v>
+        <v>7909901.72</v>
       </c>
       <c r="M191" t="n">
         <v>0</v>
       </c>
       <c r="N191" t="n">
-        <v>0</v>
+        <v>2173491.67</v>
       </c>
       <c r="O191" t="n">
-        <v>0</v>
+        <v>7909901.72</v>
       </c>
       <c r="P191" t="n">
-        <v>0</v>
+        <v>1098604.07</v>
       </c>
       <c r="Q191" t="n">
-        <v>4626</v>
+        <v>2986219</v>
       </c>
       <c r="R191" t="n">
-        <v>9991.799999999999</v>
+        <v>9727587.74</v>
       </c>
       <c r="S191" t="n">
-        <v>9864</v>
+        <v>7909901.72</v>
       </c>
       <c r="T191" t="n">
-        <v>9864</v>
+        <v>9008505.779999999</v>
       </c>
       <c r="U191" t="n">
-        <v>9991.799999999999</v>
+        <v>8628983.67</v>
       </c>
       <c r="V191" t="n">
-        <v>0</v>
+        <v>1098604.06</v>
       </c>
       <c r="W191" t="n">
-        <v>10000</v>
+        <v>8628983.67</v>
       </c>
       <c r="X191" t="n">
-        <v>10000</v>
+        <v>6455492</v>
       </c>
       <c r="Y191" t="n">
-        <v>4626</v>
+        <v>2986219</v>
       </c>
       <c r="Z191" t="n">
         <v>0</v>
       </c>
       <c r="AA191" t="n">
-        <v>10000</v>
+        <v>8628983.67</v>
       </c>
       <c r="AB191" t="n">
         <v>5</v>
@@ -27179,7 +27179,7 @@
       </c>
       <c r="AG191" t="inlineStr">
         <is>
-          <t>Premiações Culturais, Artísticas e outras</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH191" t="inlineStr">
@@ -27189,12 +27189,12 @@
       </c>
       <c r="AI191" t="inlineStr">
         <is>
-          <t>34.10.14.422.4026.4334.33903100.00.1.500.9001</t>
+          <t>34.10.14.422.4026.4334.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -27237,7 +27237,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>33903700</t>
+          <t>33903100</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -27251,7 +27251,7 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>0</v>
+        <v>9864</v>
       </c>
       <c r="M192" t="n">
         <v>0</v>
@@ -27266,37 +27266,37 @@
         <v>0</v>
       </c>
       <c r="Q192" t="n">
-        <v>0</v>
+        <v>4626</v>
       </c>
       <c r="R192" t="n">
-        <v>80612</v>
+        <v>9991.799999999999</v>
       </c>
       <c r="S192" t="n">
-        <v>0</v>
+        <v>9864</v>
       </c>
       <c r="T192" t="n">
-        <v>0</v>
+        <v>9864</v>
       </c>
       <c r="U192" t="n">
-        <v>80612</v>
+        <v>9991.799999999999</v>
       </c>
       <c r="V192" t="n">
         <v>0</v>
       </c>
       <c r="W192" t="n">
-        <v>80612</v>
+        <v>10000</v>
       </c>
       <c r="X192" t="n">
-        <v>150000</v>
+        <v>10000</v>
       </c>
       <c r="Y192" t="n">
-        <v>69388</v>
+        <v>4626</v>
       </c>
       <c r="Z192" t="n">
         <v>0</v>
       </c>
       <c r="AA192" t="n">
-        <v>150000</v>
+        <v>10000</v>
       </c>
       <c r="AB192" t="n">
         <v>5</v>
@@ -27319,7 +27319,7 @@
       </c>
       <c r="AG192" t="inlineStr">
         <is>
-          <t>Locação de Mão de Obra</t>
+          <t>Premiações Culturais, Artísticas e outras</t>
         </is>
       </c>
       <c r="AH192" t="inlineStr">
@@ -27329,12 +27329,12 @@
       </c>
       <c r="AI192" t="inlineStr">
         <is>
-          <t>34.10.14.422.4026.4334.33903700.00.1.500.9001</t>
+          <t>34.10.14.422.4026.4334.33903100.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -27377,7 +27377,7 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903700</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -27391,7 +27391,7 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>255660.84</v>
+        <v>0</v>
       </c>
       <c r="M193" t="n">
         <v>0</v>
@@ -27400,43 +27400,43 @@
         <v>0</v>
       </c>
       <c r="O193" t="n">
-        <v>255660.84</v>
+        <v>0</v>
       </c>
       <c r="P193" t="n">
-        <v>971.85</v>
+        <v>0</v>
       </c>
       <c r="Q193" t="n">
-        <v>5054381</v>
+        <v>0</v>
       </c>
       <c r="R193" t="n">
-        <v>5799481.41</v>
+        <v>80612</v>
       </c>
       <c r="S193" t="n">
-        <v>573446.41</v>
+        <v>0</v>
       </c>
       <c r="T193" t="n">
-        <v>573446.41</v>
+        <v>0</v>
       </c>
       <c r="U193" t="n">
-        <v>5798509.56</v>
+        <v>80612</v>
       </c>
       <c r="V193" t="n">
         <v>0</v>
       </c>
       <c r="W193" t="n">
-        <v>5866355</v>
+        <v>80612</v>
       </c>
       <c r="X193" t="n">
-        <v>10925362</v>
+        <v>150000</v>
       </c>
       <c r="Y193" t="n">
-        <v>5059007</v>
+        <v>69388</v>
       </c>
       <c r="Z193" t="n">
-        <v>5054381</v>
+        <v>0</v>
       </c>
       <c r="AA193" t="n">
-        <v>5870981</v>
+        <v>150000</v>
       </c>
       <c r="AB193" t="n">
         <v>5</v>
@@ -27459,7 +27459,7 @@
       </c>
       <c r="AG193" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Locação de Mão de Obra</t>
         </is>
       </c>
       <c r="AH193" t="inlineStr">
@@ -27469,12 +27469,12 @@
       </c>
       <c r="AI193" t="inlineStr">
         <is>
-          <t>34.10.14.422.4026.4334.33903900.00.1.500.9001</t>
+          <t>34.10.14.422.4026.4334.33903700.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -27527,11 +27527,11 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L194" t="n">
-        <v>266.92</v>
+        <v>255840.54</v>
       </c>
       <c r="M194" t="n">
         <v>0</v>
@@ -27540,43 +27540,43 @@
         <v>0</v>
       </c>
       <c r="O194" t="n">
-        <v>191.92</v>
+        <v>255660.84</v>
       </c>
       <c r="P194" t="n">
-        <v>925</v>
+        <v>15228.09</v>
       </c>
       <c r="Q194" t="n">
-        <v>0</v>
+        <v>5054381</v>
       </c>
       <c r="R194" t="n">
-        <v>1900</v>
+        <v>5799481.41</v>
       </c>
       <c r="S194" t="n">
-        <v>975</v>
+        <v>559190.17</v>
       </c>
       <c r="T194" t="n">
-        <v>975</v>
+        <v>573446.41</v>
       </c>
       <c r="U194" t="n">
-        <v>975</v>
+        <v>5784253.32</v>
       </c>
       <c r="V194" t="n">
-        <v>0</v>
+        <v>14256.24</v>
       </c>
       <c r="W194" t="n">
-        <v>1000</v>
+        <v>5866355</v>
       </c>
       <c r="X194" t="n">
-        <v>1000</v>
+        <v>10925362</v>
       </c>
       <c r="Y194" t="n">
-        <v>0</v>
+        <v>5059007</v>
       </c>
       <c r="Z194" t="n">
-        <v>0</v>
+        <v>5054381</v>
       </c>
       <c r="AA194" t="n">
-        <v>1000</v>
+        <v>5870981</v>
       </c>
       <c r="AB194" t="n">
         <v>5</v>
@@ -27604,17 +27604,17 @@
       </c>
       <c r="AH194" t="inlineStr">
         <is>
-          <t>Recursos destinados ao pagamento de concessionárias</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI194" t="inlineStr">
         <is>
-          <t>34.10.14.422.4026.4334.33903900.00.1.500.9006</t>
+          <t>34.10.14.422.4026.4334.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -27647,17 +27647,17 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>9025</t>
+          <t>4334</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>CPIR</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -27667,11 +27667,11 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="L195" t="n">
-        <v>0</v>
+        <v>266.92</v>
       </c>
       <c r="M195" t="n">
         <v>0</v>
@@ -27680,43 +27680,43 @@
         <v>0</v>
       </c>
       <c r="O195" t="n">
-        <v>0</v>
+        <v>191.92</v>
       </c>
       <c r="P195" t="n">
-        <v>0</v>
+        <v>925</v>
       </c>
       <c r="Q195" t="n">
-        <v>75000</v>
+        <v>0</v>
       </c>
       <c r="R195" t="n">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="S195" t="n">
-        <v>0</v>
+        <v>975</v>
       </c>
       <c r="T195" t="n">
-        <v>0</v>
+        <v>975</v>
       </c>
       <c r="U195" t="n">
-        <v>0</v>
+        <v>975</v>
       </c>
       <c r="V195" t="n">
         <v>0</v>
       </c>
       <c r="W195" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="X195" t="n">
-        <v>75000</v>
+        <v>1000</v>
       </c>
       <c r="Y195" t="n">
-        <v>75000</v>
+        <v>0</v>
       </c>
       <c r="Z195" t="n">
-        <v>75000</v>
+        <v>0</v>
       </c>
       <c r="AA195" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB195" t="n">
         <v>5</v>
@@ -27724,12 +27724,12 @@
       <c r="AC195" t="inlineStr"/>
       <c r="AD195" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>Igualdade Racial</t>
         </is>
       </c>
       <c r="AE195" t="inlineStr">
         <is>
-          <t>E2884 - Realização do Projeto "Histórias na Barra da Saia". Organização: Anderson Henrique de Olivei</t>
+          <t>CPIR - Equipamentos</t>
         </is>
       </c>
       <c r="AF195" t="inlineStr">
@@ -27739,22 +27739,22 @@
       </c>
       <c r="AG195" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH195" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Recursos destinados ao pagamento de concessionárias</t>
         </is>
       </c>
       <c r="AI195" t="inlineStr">
         <is>
-          <t>34.10.14.422.4026.9025.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4026.4334.33903900.00.1.500.9006</t>
         </is>
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -27780,24 +27780,24 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="F196" t="n">
         <v>4026</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>4322</t>
+          <t>9025</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>COPIND</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>33903600</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
@@ -27811,7 +27811,7 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>10800</v>
+        <v>0</v>
       </c>
       <c r="M196" t="n">
         <v>0</v>
@@ -27820,43 +27820,43 @@
         <v>0</v>
       </c>
       <c r="O196" t="n">
-        <v>10200</v>
+        <v>0</v>
       </c>
       <c r="P196" t="n">
-        <v>11400</v>
+        <v>0</v>
       </c>
       <c r="Q196" t="n">
-        <v>39738</v>
+        <v>75000</v>
       </c>
       <c r="R196" t="n">
-        <v>43800</v>
+        <v>0</v>
       </c>
       <c r="S196" t="n">
-        <v>31800</v>
+        <v>0</v>
       </c>
       <c r="T196" t="n">
-        <v>32400</v>
+        <v>0</v>
       </c>
       <c r="U196" t="n">
-        <v>32400</v>
+        <v>0</v>
       </c>
       <c r="V196" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="W196" t="n">
-        <v>46881</v>
+        <v>0</v>
       </c>
       <c r="X196" t="n">
-        <v>46881</v>
+        <v>75000</v>
       </c>
       <c r="Y196" t="n">
-        <v>39738</v>
+        <v>75000</v>
       </c>
       <c r="Z196" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="AA196" t="n">
-        <v>46881</v>
+        <v>0</v>
       </c>
       <c r="AB196" t="n">
         <v>5</v>
@@ -27864,12 +27864,12 @@
       <c r="AC196" t="inlineStr"/>
       <c r="AD196" t="inlineStr">
         <is>
-          <t>Povos Originários</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE196" t="inlineStr">
         <is>
-          <t>COPIND - Políticas</t>
+          <t>E2884 - Realização do Projeto "Histórias na Barra da Saia". Organização: Anderson Henrique de Olivei</t>
         </is>
       </c>
       <c r="AF196" t="inlineStr">
@@ -27879,7 +27879,7 @@
       </c>
       <c r="AG196" t="inlineStr">
         <is>
-          <t>Contratação PF</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH196" t="inlineStr">
@@ -27889,12 +27889,12 @@
       </c>
       <c r="AI196" t="inlineStr">
         <is>
-          <t>34.10.14.423.4026.4322.33903600.00.1.500.9001</t>
+          <t>34.10.14.422.4026.9025.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -27937,7 +27937,7 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903600</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -27951,7 +27951,7 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>0</v>
+        <v>10800</v>
       </c>
       <c r="M197" t="n">
         <v>0</v>
@@ -27960,43 +27960,43 @@
         <v>0</v>
       </c>
       <c r="O197" t="n">
-        <v>0</v>
+        <v>10200</v>
       </c>
       <c r="P197" t="n">
-        <v>19140.97</v>
+        <v>11400</v>
       </c>
       <c r="Q197" t="n">
-        <v>0</v>
+        <v>39738</v>
       </c>
       <c r="R197" t="n">
-        <v>52809.97</v>
+        <v>43800</v>
       </c>
       <c r="S197" t="n">
-        <v>0</v>
+        <v>31800</v>
       </c>
       <c r="T197" t="n">
-        <v>0</v>
+        <v>32400</v>
       </c>
       <c r="U197" t="n">
-        <v>33669</v>
+        <v>32400</v>
       </c>
       <c r="V197" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="W197" t="n">
-        <v>33669</v>
+        <v>46881</v>
       </c>
       <c r="X197" t="n">
-        <v>220966</v>
+        <v>46881</v>
       </c>
       <c r="Y197" t="n">
-        <v>187297</v>
+        <v>39738</v>
       </c>
       <c r="Z197" t="n">
         <v>0</v>
       </c>
       <c r="AA197" t="n">
-        <v>220966</v>
+        <v>46881</v>
       </c>
       <c r="AB197" t="n">
         <v>5</v>
@@ -28019,7 +28019,7 @@
       </c>
       <c r="AG197" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Contratação PF</t>
         </is>
       </c>
       <c r="AH197" t="inlineStr">
@@ -28029,12 +28029,12 @@
       </c>
       <c r="AI197" t="inlineStr">
         <is>
-          <t>34.10.14.423.4026.4322.33903900.00.1.500.9001</t>
+          <t>34.10.14.423.4026.4322.33903600.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -28067,17 +28067,17 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>9234</t>
+          <t>4322</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>COPIND</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -28103,13 +28103,13 @@
         <v>0</v>
       </c>
       <c r="P198" t="n">
-        <v>0</v>
+        <v>19140.97</v>
       </c>
       <c r="Q198" t="n">
-        <v>155746.65</v>
+        <v>0</v>
       </c>
       <c r="R198" t="n">
-        <v>0</v>
+        <v>52809.97</v>
       </c>
       <c r="S198" t="n">
         <v>0</v>
@@ -28118,25 +28118,25 @@
         <v>0</v>
       </c>
       <c r="U198" t="n">
-        <v>0</v>
+        <v>33669</v>
       </c>
       <c r="V198" t="n">
         <v>0</v>
       </c>
       <c r="W198" t="n">
-        <v>0</v>
+        <v>33669</v>
       </c>
       <c r="X198" t="n">
-        <v>100000</v>
+        <v>220966</v>
       </c>
       <c r="Y198" t="n">
-        <v>155747.3</v>
+        <v>187297</v>
       </c>
       <c r="Z198" t="n">
-        <v>99999.35000000001</v>
+        <v>0</v>
       </c>
       <c r="AA198" t="n">
-        <v>0.65</v>
+        <v>220966</v>
       </c>
       <c r="AB198" t="n">
         <v>5</v>
@@ -28144,12 +28144,12 @@
       <c r="AC198" t="inlineStr"/>
       <c r="AD198" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>Povos Originários</t>
         </is>
       </c>
       <c r="AE198" t="inlineStr">
         <is>
-          <t xml:space="preserve">E2873 - Realização do Projeto "Observatório Indígena"- Organização: Aliança Universidade e os Povos </t>
+          <t>COPIND - Políticas</t>
         </is>
       </c>
       <c r="AF198" t="inlineStr">
@@ -28159,7 +28159,7 @@
       </c>
       <c r="AG198" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH198" t="inlineStr">
@@ -28169,12 +28169,12 @@
       </c>
       <c r="AI198" t="inlineStr">
         <is>
-          <t>34.10.14.423.4026.9234.33503900.00.1.500.9001</t>
+          <t>34.10.14.423.4026.4322.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -28186,12 +28186,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>FUMCAF</t>
+          <t>SMDHC</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -28200,19 +28200,19 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F199" t="n">
-        <v>4010</v>
+        <v>4026</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>9234</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>SESANA</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -28227,7 +28227,7 @@
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>7047</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L199" t="n">
@@ -28246,7 +28246,7 @@
         <v>0</v>
       </c>
       <c r="Q199" t="n">
-        <v>0</v>
+        <v>155746.65</v>
       </c>
       <c r="R199" t="n">
         <v>0</v>
@@ -28267,16 +28267,16 @@
         <v>0</v>
       </c>
       <c r="X199" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="Y199" t="n">
-        <v>0</v>
+        <v>155747.3</v>
       </c>
       <c r="Z199" t="n">
-        <v>0</v>
+        <v>99999.35000000001</v>
       </c>
       <c r="AA199" t="n">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="AB199" t="n">
         <v>5</v>
@@ -28284,12 +28284,12 @@
       <c r="AC199" t="inlineStr"/>
       <c r="AD199" t="inlineStr">
         <is>
-          <t>Segurança Alimentar</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE199" t="inlineStr">
         <is>
-          <t>SESANA - Políticas</t>
+          <t xml:space="preserve">E2873 - Realização do Projeto "Observatório Indígena"- Organização: Aliança Universidade e os Povos </t>
         </is>
       </c>
       <c r="AF199" t="inlineStr">
@@ -28304,17 +28304,17 @@
       </c>
       <c r="AH199" t="inlineStr">
         <is>
-          <t>Emendas Parlamentares - Silvia Ferraro</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI199" t="inlineStr">
         <is>
-          <t>34.20.14.422.4010.4426.33503900.00.1.500.7047</t>
+          <t>34.10.14.423.4026.9234.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -28367,20 +28367,20 @@
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>7069</t>
+          <t>7047</t>
         </is>
       </c>
       <c r="L200" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="M200" t="n">
         <v>0</v>
       </c>
       <c r="N200" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="O200" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="P200" t="n">
         <v>0</v>
@@ -28389,22 +28389,22 @@
         <v>0</v>
       </c>
       <c r="R200" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="S200" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="T200" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="U200" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="V200" t="n">
         <v>0</v>
       </c>
       <c r="W200" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="X200" t="n">
         <v>0</v>
@@ -28416,7 +28416,7 @@
         <v>0</v>
       </c>
       <c r="AA200" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="AB200" t="n">
         <v>5</v>
@@ -28444,17 +28444,17 @@
       </c>
       <c r="AH200" t="inlineStr">
         <is>
-          <t>Emendas Parlamentares - Amanda Vettorazzo</t>
+          <t>Emendas Parlamentares - Silvia Ferraro</t>
         </is>
       </c>
       <c r="AI200" t="inlineStr">
         <is>
-          <t>34.20.14.422.4010.4426.33503900.00.1.500.7069</t>
+          <t>34.20.14.422.4010.4426.33503900.00.1.500.7047</t>
         </is>
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -28507,20 +28507,20 @@
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>7079</t>
+          <t>7069</t>
         </is>
       </c>
       <c r="L201" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="M201" t="n">
         <v>0</v>
       </c>
       <c r="N201" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="O201" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="P201" t="n">
         <v>0</v>
@@ -28529,22 +28529,22 @@
         <v>0</v>
       </c>
       <c r="R201" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="S201" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="T201" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="U201" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="V201" t="n">
         <v>0</v>
       </c>
       <c r="W201" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="X201" t="n">
         <v>0</v>
@@ -28556,7 +28556,7 @@
         <v>0</v>
       </c>
       <c r="AA201" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="AB201" t="n">
         <v>5</v>
@@ -28584,17 +28584,17 @@
       </c>
       <c r="AH201" t="inlineStr">
         <is>
-          <t>Emendas Parlamentares - Marina Bragante</t>
+          <t>Emendas Parlamentares - Amanda Vettorazzo</t>
         </is>
       </c>
       <c r="AI201" t="inlineStr">
         <is>
-          <t>34.20.14.422.4010.4426.33503900.00.1.500.7079</t>
+          <t>34.20.14.422.4010.4426.33503900.00.1.500.7069</t>
         </is>
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -28637,7 +28637,7 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -28647,7 +28647,7 @@
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>7079</t>
         </is>
       </c>
       <c r="L202" t="n">
@@ -28657,7 +28657,7 @@
         <v>0</v>
       </c>
       <c r="N202" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="O202" t="n">
         <v>0</v>
@@ -28684,19 +28684,19 @@
         <v>0</v>
       </c>
       <c r="W202" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="X202" t="n">
-        <v>589773</v>
+        <v>0</v>
       </c>
       <c r="Y202" t="n">
-        <v>589773</v>
+        <v>0</v>
       </c>
       <c r="Z202" t="n">
         <v>0</v>
       </c>
       <c r="AA202" t="n">
-        <v>589773</v>
+        <v>200000</v>
       </c>
       <c r="AB202" t="n">
         <v>5</v>
@@ -28719,65 +28719,65 @@
       </c>
       <c r="AG202" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH202" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Emendas Parlamentares - Marina Bragante</t>
         </is>
       </c>
       <c r="AI202" t="inlineStr">
         <is>
-          <t>34.20.14.422.4010.4426.33903900.00.1.500.9001</t>
+          <t>34.20.14.422.4010.4426.33503900.00.1.500.7079</t>
         </is>
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>FAASP</t>
+          <t>FUMCAF</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>244</v>
+        <v>422</v>
       </c>
       <c r="F203" t="n">
         <v>4010</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>4302</t>
+          <t>4426</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>FAASP</t>
+          <t>SESANA</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -28791,16 +28791,16 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>30296477.82</v>
+        <v>0</v>
       </c>
       <c r="M203" t="n">
         <v>0</v>
       </c>
       <c r="N203" t="n">
-        <v>5086650.13</v>
+        <v>0</v>
       </c>
       <c r="O203" t="n">
-        <v>30296477.82</v>
+        <v>0</v>
       </c>
       <c r="P203" t="n">
         <v>0</v>
@@ -28809,34 +28809,34 @@
         <v>0</v>
       </c>
       <c r="R203" t="n">
-        <v>45922205.13</v>
+        <v>0</v>
       </c>
       <c r="S203" t="n">
-        <v>45922205.12</v>
+        <v>0</v>
       </c>
       <c r="T203" t="n">
-        <v>45922205.12</v>
+        <v>0</v>
       </c>
       <c r="U203" t="n">
-        <v>45922205.13</v>
+        <v>0</v>
       </c>
       <c r="V203" t="n">
         <v>0</v>
       </c>
       <c r="W203" t="n">
-        <v>45922205.13</v>
+        <v>0</v>
       </c>
       <c r="X203" t="n">
-        <v>40835555</v>
+        <v>589773</v>
       </c>
       <c r="Y203" t="n">
-        <v>0</v>
+        <v>589773</v>
       </c>
       <c r="Z203" t="n">
         <v>0</v>
       </c>
       <c r="AA203" t="n">
-        <v>45922205.13</v>
+        <v>589773</v>
       </c>
       <c r="AB203" t="n">
         <v>5</v>
@@ -28849,7 +28849,7 @@
       </c>
       <c r="AE203" t="inlineStr">
         <is>
-          <t>FAASP</t>
+          <t>SESANA - Políticas</t>
         </is>
       </c>
       <c r="AF203" t="inlineStr">
@@ -28859,7 +28859,7 @@
       </c>
       <c r="AG203" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH203" t="inlineStr">
@@ -28869,12 +28869,12 @@
       </c>
       <c r="AI203" t="inlineStr">
         <is>
-          <t>78.10.08.244.4010.4302.33503900.00.1.500.9001</t>
+          <t>34.20.14.422.4010.4426.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -28917,7 +28917,7 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>44905100</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -28931,16 +28931,16 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>0</v>
+        <v>30296477.82</v>
       </c>
       <c r="M204" t="n">
         <v>0</v>
       </c>
       <c r="N204" t="n">
-        <v>0</v>
+        <v>5086650.13</v>
       </c>
       <c r="O204" t="n">
-        <v>0</v>
+        <v>30296477.82</v>
       </c>
       <c r="P204" t="n">
         <v>0</v>
@@ -28949,34 +28949,34 @@
         <v>0</v>
       </c>
       <c r="R204" t="n">
-        <v>0</v>
+        <v>45922205.13</v>
       </c>
       <c r="S204" t="n">
-        <v>0</v>
+        <v>45922205.12</v>
       </c>
       <c r="T204" t="n">
-        <v>0</v>
+        <v>45922205.12</v>
       </c>
       <c r="U204" t="n">
-        <v>0</v>
+        <v>45922205.13</v>
       </c>
       <c r="V204" t="n">
         <v>0</v>
       </c>
       <c r="W204" t="n">
-        <v>600437</v>
+        <v>45922205.13</v>
       </c>
       <c r="X204" t="n">
-        <v>16896102</v>
+        <v>40835555</v>
       </c>
       <c r="Y204" t="n">
-        <v>16295665</v>
+        <v>0</v>
       </c>
       <c r="Z204" t="n">
         <v>0</v>
       </c>
       <c r="AA204" t="n">
-        <v>16896102</v>
+        <v>45922205.13</v>
       </c>
       <c r="AB204" t="n">
         <v>5</v>
@@ -28999,7 +28999,7 @@
       </c>
       <c r="AG204" t="inlineStr">
         <is>
-          <t>Obras e Instalações</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH204" t="inlineStr">
@@ -29009,12 +29009,12 @@
       </c>
       <c r="AI204" t="inlineStr">
         <is>
-          <t>78.10.08.244.4010.4302.44905100.00.1.500.9001</t>
+          <t>78.10.08.244.4010.4302.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -29036,23 +29036,23 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>08</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>122</v>
+        <v>244</v>
       </c>
       <c r="F205" t="n">
-        <v>4001</v>
+        <v>4010</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>3002</t>
+          <t>4302</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>SESANA</t>
+          <t>FAASP</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -29104,19 +29104,19 @@
         <v>0</v>
       </c>
       <c r="W205" t="n">
-        <v>1000</v>
+        <v>600437</v>
       </c>
       <c r="X205" t="n">
-        <v>1000</v>
+        <v>16896102</v>
       </c>
       <c r="Y205" t="n">
-        <v>0</v>
+        <v>16295665</v>
       </c>
       <c r="Z205" t="n">
         <v>0</v>
       </c>
       <c r="AA205" t="n">
-        <v>1000</v>
+        <v>16896102</v>
       </c>
       <c r="AB205" t="n">
         <v>5</v>
@@ -29129,7 +29129,7 @@
       </c>
       <c r="AE205" t="inlineStr">
         <is>
-          <t>Sesana - Reformas</t>
+          <t>FAASP</t>
         </is>
       </c>
       <c r="AF205" t="inlineStr">
@@ -29149,12 +29149,12 @@
       </c>
       <c r="AI205" t="inlineStr">
         <is>
-          <t>78.10.14.122.4001.3002.44905100.00.1.500.9001</t>
+          <t>78.10.08.244.4010.4302.44905100.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -29197,7 +29197,7 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>44906100</t>
+          <t>44905100</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -29217,7 +29217,7 @@
         <v>0</v>
       </c>
       <c r="N206" t="n">
-        <v>361510</v>
+        <v>0</v>
       </c>
       <c r="O206" t="n">
         <v>0</v>
@@ -29229,7 +29229,7 @@
         <v>0</v>
       </c>
       <c r="R206" t="n">
-        <v>361510</v>
+        <v>0</v>
       </c>
       <c r="S206" t="n">
         <v>0</v>
@@ -29238,16 +29238,16 @@
         <v>0</v>
       </c>
       <c r="U206" t="n">
-        <v>361510</v>
+        <v>0</v>
       </c>
       <c r="V206" t="n">
         <v>0</v>
       </c>
       <c r="W206" t="n">
-        <v>361510</v>
+        <v>1000</v>
       </c>
       <c r="X206" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y206" t="n">
         <v>0</v>
@@ -29256,7 +29256,7 @@
         <v>0</v>
       </c>
       <c r="AA206" t="n">
-        <v>361510</v>
+        <v>1000</v>
       </c>
       <c r="AB206" t="n">
         <v>5</v>
@@ -29279,7 +29279,7 @@
       </c>
       <c r="AG206" t="inlineStr">
         <is>
-          <t>Aquisição de Imóveis</t>
+          <t>Obras e Instalações</t>
         </is>
       </c>
       <c r="AH206" t="inlineStr">
@@ -29289,12 +29289,12 @@
       </c>
       <c r="AI206" t="inlineStr">
         <is>
-          <t>78.10.14.122.4001.3002.44906100.00.1.500.9001</t>
+          <t>78.10.14.122.4001.3002.44905100.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -29320,14 +29320,14 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>422</v>
+        <v>122</v>
       </c>
       <c r="F207" t="n">
-        <v>4010</v>
+        <v>4001</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>3002</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -29337,7 +29337,7 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>44906100</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -29351,52 +29351,52 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>118161204.58</v>
+        <v>0</v>
       </c>
       <c r="M207" t="n">
         <v>0</v>
       </c>
       <c r="N207" t="n">
-        <v>0</v>
+        <v>361510</v>
       </c>
       <c r="O207" t="n">
-        <v>117374145.55</v>
+        <v>0</v>
       </c>
       <c r="P207" t="n">
-        <v>49808521.04</v>
+        <v>0</v>
       </c>
       <c r="Q207" t="n">
-        <v>5086650.13</v>
+        <v>0</v>
       </c>
       <c r="R207" t="n">
-        <v>214390827.19</v>
+        <v>361510</v>
       </c>
       <c r="S207" t="n">
-        <v>147596374.05</v>
+        <v>0</v>
       </c>
       <c r="T207" t="n">
-        <v>153263750.29</v>
+        <v>0</v>
       </c>
       <c r="U207" t="n">
-        <v>164582306.15</v>
+        <v>361510</v>
       </c>
       <c r="V207" t="n">
-        <v>5667376.24</v>
+        <v>0</v>
       </c>
       <c r="W207" t="n">
-        <v>165715582</v>
+        <v>361510</v>
       </c>
       <c r="X207" t="n">
-        <v>171813039</v>
+        <v>0</v>
       </c>
       <c r="Y207" t="n">
-        <v>5735947</v>
+        <v>0</v>
       </c>
       <c r="Z207" t="n">
-        <v>5448160.13</v>
+        <v>0</v>
       </c>
       <c r="AA207" t="n">
-        <v>166364878.87</v>
+        <v>361510</v>
       </c>
       <c r="AB207" t="n">
         <v>5</v>
@@ -29409,7 +29409,7 @@
       </c>
       <c r="AE207" t="inlineStr">
         <is>
-          <t>SESANA - Políticas</t>
+          <t>Sesana - Reformas</t>
         </is>
       </c>
       <c r="AF207" t="inlineStr">
@@ -29419,7 +29419,7 @@
       </c>
       <c r="AG207" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Aquisição de Imóveis</t>
         </is>
       </c>
       <c r="AH207" t="inlineStr">
@@ -29429,12 +29429,12 @@
       </c>
       <c r="AI207" t="inlineStr">
         <is>
-          <t>78.10.14.422.4010.4426.33503900.00.1.500.9001</t>
+          <t>78.10.14.122.4001.3002.44906100.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -29477,21 +29477,21 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>00</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L208" t="n">
-        <v>0</v>
+        <v>118180673.01</v>
       </c>
       <c r="M208" t="n">
         <v>0</v>
@@ -29500,43 +29500,43 @@
         <v>0</v>
       </c>
       <c r="O208" t="n">
-        <v>0</v>
+        <v>117374145.55</v>
       </c>
       <c r="P208" t="n">
-        <v>0</v>
+        <v>49808521.04</v>
       </c>
       <c r="Q208" t="n">
-        <v>0</v>
+        <v>5086650.13</v>
       </c>
       <c r="R208" t="n">
-        <v>0</v>
+        <v>214390827.19</v>
       </c>
       <c r="S208" t="n">
-        <v>0</v>
+        <v>153077170.3</v>
       </c>
       <c r="T208" t="n">
-        <v>0</v>
+        <v>158744546.54</v>
       </c>
       <c r="U208" t="n">
-        <v>0</v>
+        <v>164582306.15</v>
       </c>
       <c r="V208" t="n">
-        <v>0</v>
+        <v>5667376.24</v>
       </c>
       <c r="W208" t="n">
-        <v>2000</v>
+        <v>165715582</v>
       </c>
       <c r="X208" t="n">
-        <v>2000</v>
+        <v>171813039</v>
       </c>
       <c r="Y208" t="n">
-        <v>0</v>
+        <v>5735947</v>
       </c>
       <c r="Z208" t="n">
-        <v>0</v>
+        <v>5448160.13</v>
       </c>
       <c r="AA208" t="n">
-        <v>2000</v>
+        <v>166364878.87</v>
       </c>
       <c r="AB208" t="n">
         <v>5</v>
@@ -29554,27 +29554,27 @@
       </c>
       <c r="AF208" t="inlineStr">
         <is>
-          <t>05 - Outras Fontes</t>
+          <t>00 - Tesouro Municipal</t>
         </is>
       </c>
       <c r="AG208" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH208" t="inlineStr">
         <is>
-          <t>PMSP-SMDU/CIDADE SOLIDÁRIA</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI208" t="inlineStr">
         <is>
-          <t>78.10.14.422.4010.4426.33903000.05.1.799.1268</t>
+          <t>78.10.14.422.4010.4426.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -29622,12 +29622,12 @@
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>05</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="L209" t="n">
@@ -29664,10 +29664,10 @@
         <v>0</v>
       </c>
       <c r="W209" t="n">
-        <v>11298</v>
+        <v>2000</v>
       </c>
       <c r="X209" t="n">
-        <v>11298</v>
+        <v>2000</v>
       </c>
       <c r="Y209" t="n">
         <v>0</v>
@@ -29676,7 +29676,7 @@
         <v>0</v>
       </c>
       <c r="AA209" t="n">
-        <v>11298</v>
+        <v>2000</v>
       </c>
       <c r="AB209" t="n">
         <v>5</v>
@@ -29694,7 +29694,7 @@
       </c>
       <c r="AF209" t="inlineStr">
         <is>
-          <t>08 - Recusos Vinculados</t>
+          <t>05 - Outras Fontes</t>
         </is>
       </c>
       <c r="AG209" t="inlineStr">
@@ -29704,17 +29704,17 @@
       </c>
       <c r="AH209" t="inlineStr">
         <is>
-          <t>PMSP-SMDHC-Fundo Munic.de Abastecimento Alimentar de São Paulo-FAASP</t>
+          <t>PMSP-SMDU/CIDADE SOLIDÁRIA</t>
         </is>
       </c>
       <c r="AI209" t="inlineStr">
         <is>
-          <t>78.10.14.422.4010.4426.33903000.08.1.759.1416</t>
+          <t>78.10.14.422.4010.4426.33903000.05.1.799.1268</t>
         </is>
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -29757,21 +29757,21 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>33903200</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>08</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>1416</t>
         </is>
       </c>
       <c r="L210" t="n">
-        <v>62273213.71</v>
+        <v>0</v>
       </c>
       <c r="M210" t="n">
         <v>0</v>
@@ -29780,43 +29780,43 @@
         <v>0</v>
       </c>
       <c r="O210" t="n">
-        <v>60344741.71</v>
+        <v>0</v>
       </c>
       <c r="P210" t="n">
-        <v>62818272</v>
+        <v>0</v>
       </c>
       <c r="Q210" t="n">
         <v>0</v>
       </c>
       <c r="R210" t="n">
-        <v>199707294</v>
+        <v>0</v>
       </c>
       <c r="S210" t="n">
-        <v>113049655.2</v>
+        <v>0</v>
       </c>
       <c r="T210" t="n">
-        <v>113049655.2</v>
+        <v>0</v>
       </c>
       <c r="U210" t="n">
-        <v>136889022</v>
+        <v>0</v>
       </c>
       <c r="V210" t="n">
         <v>0</v>
       </c>
       <c r="W210" t="n">
-        <v>136889022</v>
+        <v>11298</v>
       </c>
       <c r="X210" t="n">
-        <v>141616875</v>
+        <v>11298</v>
       </c>
       <c r="Y210" t="n">
-        <v>4727853</v>
+        <v>0</v>
       </c>
       <c r="Z210" t="n">
         <v>0</v>
       </c>
       <c r="AA210" t="n">
-        <v>141616875</v>
+        <v>11298</v>
       </c>
       <c r="AB210" t="n">
         <v>5</v>
@@ -29834,27 +29834,27 @@
       </c>
       <c r="AF210" t="inlineStr">
         <is>
-          <t>00 - Tesouro Municipal</t>
+          <t>08 - Recusos Vinculados</t>
         </is>
       </c>
       <c r="AG210" t="inlineStr">
         <is>
-          <t>Cestas Básicas</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AH210" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>PMSP-SMDHC-Fundo Munic.de Abastecimento Alimentar de São Paulo-FAASP</t>
         </is>
       </c>
       <c r="AI210" t="inlineStr">
         <is>
-          <t>78.10.14.422.4010.4426.33903200.00.1.500.9001</t>
+          <t>78.10.14.422.4010.4426.33903000.08.1.759.1416</t>
         </is>
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -29897,7 +29897,7 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903200</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
@@ -29911,7 +29911,7 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>47621025.9</v>
+        <v>62273213.71</v>
       </c>
       <c r="M211" t="n">
         <v>0</v>
@@ -29920,43 +29920,43 @@
         <v>0</v>
       </c>
       <c r="O211" t="n">
-        <v>47261773.84</v>
+        <v>60344741.71</v>
       </c>
       <c r="P211" t="n">
-        <v>50438263.91</v>
+        <v>62818272</v>
       </c>
       <c r="Q211" t="n">
         <v>0</v>
       </c>
       <c r="R211" t="n">
-        <v>129881289.91</v>
+        <v>199707294</v>
       </c>
       <c r="S211" t="n">
-        <v>78962487.98999999</v>
+        <v>113049655.2</v>
       </c>
       <c r="T211" t="n">
-        <v>99116487.98999999</v>
+        <v>113049655.2</v>
       </c>
       <c r="U211" t="n">
-        <v>79443026</v>
+        <v>136889022</v>
       </c>
       <c r="V211" t="n">
-        <v>20154000</v>
+        <v>0</v>
       </c>
       <c r="W211" t="n">
-        <v>79443026</v>
+        <v>136889022</v>
       </c>
       <c r="X211" t="n">
-        <v>83642123</v>
+        <v>141616875</v>
       </c>
       <c r="Y211" t="n">
-        <v>2792377</v>
+        <v>4727853</v>
       </c>
       <c r="Z211" t="n">
-        <v>1406720</v>
+        <v>0</v>
       </c>
       <c r="AA211" t="n">
-        <v>82235403</v>
+        <v>141616875</v>
       </c>
       <c r="AB211" t="n">
         <v>5</v>
@@ -29979,7 +29979,7 @@
       </c>
       <c r="AG211" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Cestas Básicas</t>
         </is>
       </c>
       <c r="AH211" t="inlineStr">
@@ -29989,12 +29989,12 @@
       </c>
       <c r="AI211" t="inlineStr">
         <is>
-          <t>78.10.14.422.4010.4426.33903900.00.1.500.9001</t>
+          <t>78.10.14.422.4010.4426.33903200.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -30042,16 +30042,16 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>00</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L212" t="n">
-        <v>0</v>
+        <v>47775619.8</v>
       </c>
       <c r="M212" t="n">
         <v>0</v>
@@ -30060,43 +30060,43 @@
         <v>0</v>
       </c>
       <c r="O212" t="n">
-        <v>0</v>
+        <v>47261773.84</v>
       </c>
       <c r="P212" t="n">
-        <v>0</v>
+        <v>50438263.91</v>
       </c>
       <c r="Q212" t="n">
         <v>0</v>
       </c>
       <c r="R212" t="n">
-        <v>0</v>
+        <v>129881289.91</v>
       </c>
       <c r="S212" t="n">
-        <v>0</v>
+        <v>79232487.98999999</v>
       </c>
       <c r="T212" t="n">
-        <v>0</v>
+        <v>99386487.98999999</v>
       </c>
       <c r="U212" t="n">
-        <v>0</v>
+        <v>79443026</v>
       </c>
       <c r="V212" t="n">
-        <v>0</v>
+        <v>20154000</v>
       </c>
       <c r="W212" t="n">
-        <v>2000</v>
+        <v>79443026</v>
       </c>
       <c r="X212" t="n">
-        <v>2000</v>
+        <v>83642123</v>
       </c>
       <c r="Y212" t="n">
-        <v>0</v>
+        <v>2792377</v>
       </c>
       <c r="Z212" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="AA212" t="n">
-        <v>2000</v>
+        <v>82235403</v>
       </c>
       <c r="AB212" t="n">
         <v>5</v>
@@ -30114,7 +30114,7 @@
       </c>
       <c r="AF212" t="inlineStr">
         <is>
-          <t>08 - Recusos Vinculados</t>
+          <t>00 - Tesouro Municipal</t>
         </is>
       </c>
       <c r="AG212" t="inlineStr">
@@ -30124,17 +30124,17 @@
       </c>
       <c r="AH212" t="inlineStr">
         <is>
-          <t>Repasse nº 970993/2025-Banco de Alimentos</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI212" t="inlineStr">
         <is>
-          <t>78.10.14.422.4010.4426.33903900.08.1.759.1796</t>
+          <t>78.10.14.422.4010.4426.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -30177,30 +30177,30 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>33913900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>08</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="L213" t="n">
-        <v>784000</v>
+        <v>0</v>
       </c>
       <c r="M213" t="n">
         <v>0</v>
       </c>
       <c r="N213" t="n">
-        <v>1406720</v>
+        <v>0</v>
       </c>
       <c r="O213" t="n">
-        <v>672000</v>
+        <v>0</v>
       </c>
       <c r="P213" t="n">
         <v>0</v>
@@ -30209,25 +30209,25 @@
         <v>0</v>
       </c>
       <c r="R213" t="n">
-        <v>1406720</v>
+        <v>0</v>
       </c>
       <c r="S213" t="n">
-        <v>1406720</v>
+        <v>0</v>
       </c>
       <c r="T213" t="n">
-        <v>1406720</v>
+        <v>0</v>
       </c>
       <c r="U213" t="n">
-        <v>1406720</v>
+        <v>0</v>
       </c>
       <c r="V213" t="n">
         <v>0</v>
       </c>
       <c r="W213" t="n">
-        <v>1406720</v>
+        <v>2000</v>
       </c>
       <c r="X213" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="Y213" t="n">
         <v>0</v>
@@ -30236,7 +30236,7 @@
         <v>0</v>
       </c>
       <c r="AA213" t="n">
-        <v>1406720</v>
+        <v>2000</v>
       </c>
       <c r="AB213" t="n">
         <v>5</v>
@@ -30254,39 +30254,39 @@
       </c>
       <c r="AF213" t="inlineStr">
         <is>
-          <t>00 - Tesouro Municipal</t>
+          <t>08 - Recusos Vinculados</t>
         </is>
       </c>
       <c r="AG213" t="inlineStr">
         <is>
-          <t>Transferência entre Órgãos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH213" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Repasse nº 970993/2025-Banco de Alimentos</t>
         </is>
       </c>
       <c r="AI213" t="inlineStr">
         <is>
-          <t>78.10.14.422.4010.4426.33913900.00.1.500.9001</t>
+          <t>78.10.14.422.4010.4426.33903900.08.1.759.1796</t>
         </is>
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>78</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>FUMCAD</t>
+          <t>FAASP</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -30300,24 +30300,24 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>122</v>
+        <v>422</v>
       </c>
       <c r="F214" t="n">
-        <v>4004</v>
+        <v>4010</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>2803</t>
+          <t>4426</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Conselho</t>
+          <t>SESANA</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33913900</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
@@ -30331,16 +30331,16 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>0</v>
+        <v>784000</v>
       </c>
       <c r="M214" t="n">
         <v>0</v>
       </c>
       <c r="N214" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="O214" t="n">
-        <v>0</v>
+        <v>672000</v>
       </c>
       <c r="P214" t="n">
         <v>0</v>
@@ -30349,25 +30349,25 @@
         <v>0</v>
       </c>
       <c r="R214" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="S214" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="T214" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="U214" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="V214" t="n">
         <v>0</v>
       </c>
       <c r="W214" t="n">
-        <v>3000</v>
+        <v>1406720</v>
       </c>
       <c r="X214" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="Y214" t="n">
         <v>0</v>
@@ -30376,7 +30376,7 @@
         <v>0</v>
       </c>
       <c r="AA214" t="n">
-        <v>3000</v>
+        <v>1406720</v>
       </c>
       <c r="AB214" t="n">
         <v>5</v>
@@ -30384,12 +30384,12 @@
       <c r="AC214" t="inlineStr"/>
       <c r="AD214" t="inlineStr">
         <is>
-          <t>Conselho</t>
+          <t>Segurança Alimentar</t>
         </is>
       </c>
       <c r="AE214" t="inlineStr">
         <is>
-          <t>Conselho</t>
+          <t>SESANA - Políticas</t>
         </is>
       </c>
       <c r="AF214" t="inlineStr">
@@ -30399,7 +30399,7 @@
       </c>
       <c r="AG214" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Transferência entre Órgãos</t>
         </is>
       </c>
       <c r="AH214" t="inlineStr">
@@ -30409,12 +30409,12 @@
       </c>
       <c r="AI214" t="inlineStr">
         <is>
-          <t>90.10.14.122.4004.2803.33903000.00.1.500.9001</t>
+          <t>78.10.14.422.4010.4426.33913900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -30457,7 +30457,7 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
@@ -30504,10 +30504,10 @@
         <v>0</v>
       </c>
       <c r="W215" t="n">
-        <v>6245</v>
+        <v>3000</v>
       </c>
       <c r="X215" t="n">
-        <v>6245</v>
+        <v>3000</v>
       </c>
       <c r="Y215" t="n">
         <v>0</v>
@@ -30516,7 +30516,7 @@
         <v>0</v>
       </c>
       <c r="AA215" t="n">
-        <v>6245</v>
+        <v>3000</v>
       </c>
       <c r="AB215" t="n">
         <v>5</v>
@@ -30539,7 +30539,7 @@
       </c>
       <c r="AG215" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AH215" t="inlineStr">
@@ -30549,12 +30549,12 @@
       </c>
       <c r="AI215" t="inlineStr">
         <is>
-          <t>90.10.14.122.4004.2803.33903900.00.1.500.9001</t>
+          <t>90.10.14.122.4004.2803.33903000.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -30580,24 +30580,24 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F216" t="n">
-        <v>4002</v>
+        <v>4004</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>1220</t>
+          <t>2803</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>DTIC</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>44904000</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
@@ -30644,10 +30644,10 @@
         <v>0</v>
       </c>
       <c r="W216" t="n">
-        <v>1000</v>
+        <v>6245</v>
       </c>
       <c r="X216" t="n">
-        <v>1000</v>
+        <v>6245</v>
       </c>
       <c r="Y216" t="n">
         <v>0</v>
@@ -30656,7 +30656,7 @@
         <v>0</v>
       </c>
       <c r="AA216" t="n">
-        <v>1000</v>
+        <v>6245</v>
       </c>
       <c r="AB216" t="n">
         <v>5</v>
@@ -30664,12 +30664,12 @@
       <c r="AC216" t="inlineStr"/>
       <c r="AD216" t="inlineStr">
         <is>
-          <t>Tecnologia</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="AE216" t="inlineStr">
         <is>
-          <t>DTIC - Desenvolvimento</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="AF216" t="inlineStr">
@@ -30679,7 +30679,7 @@
       </c>
       <c r="AG216" t="inlineStr">
         <is>
-          <t>Serviços de Tecnologia da Informação e Comunicação Permanente - PJ</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH216" t="inlineStr">
@@ -30689,12 +30689,12 @@
       </c>
       <c r="AI216" t="inlineStr">
         <is>
-          <t>90.10.14.126.4002.1220.44904000.00.1.500.9001</t>
+          <t>90.10.14.122.4004.2803.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -30720,24 +30720,24 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>422</v>
+        <v>126</v>
       </c>
       <c r="F217" t="n">
-        <v>4019</v>
+        <v>4002</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>6160</t>
+          <t>1220</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>FUMCAD</t>
+          <t>DTIC</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>44904000</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
@@ -30747,7 +30747,7 @@
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>0004</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L217" t="n">
@@ -30784,10 +30784,10 @@
         <v>0</v>
       </c>
       <c r="W217" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="X217" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y217" t="n">
         <v>0</v>
@@ -30796,7 +30796,7 @@
         <v>0</v>
       </c>
       <c r="AA217" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB217" t="n">
         <v>5</v>
@@ -30804,12 +30804,12 @@
       <c r="AC217" t="inlineStr"/>
       <c r="AD217" t="inlineStr">
         <is>
-          <t>Criança e Adolescente</t>
+          <t>Tecnologia</t>
         </is>
       </c>
       <c r="AE217" t="inlineStr">
         <is>
-          <t>FUMCAD</t>
+          <t>DTIC - Desenvolvimento</t>
         </is>
       </c>
       <c r="AF217" t="inlineStr">
@@ -30819,22 +30819,22 @@
       </c>
       <c r="AG217" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Serviços de Tecnologia da Informação e Comunicação Permanente - PJ</t>
         </is>
       </c>
       <c r="AH217" t="inlineStr">
         <is>
-          <t>Recursos do FUMCAD desvinculados</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI217" t="inlineStr">
         <is>
-          <t>90.10.14.422.4019.6160.33503900.00.1.501.0004</t>
+          <t>90.10.14.126.4002.1220.44904000.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>10/08/2026 07:34:19</t>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>
@@ -30882,16 +30882,16 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>00</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>0958</t>
+          <t>0004</t>
         </is>
       </c>
       <c r="L218" t="n">
-        <v>34621230.63</v>
+        <v>0</v>
       </c>
       <c r="M218" t="n">
         <v>0</v>
@@ -30900,34 +30900,34 @@
         <v>0</v>
       </c>
       <c r="O218" t="n">
-        <v>33234725.6</v>
+        <v>0</v>
       </c>
       <c r="P218" t="n">
-        <v>6388346.56</v>
+        <v>0</v>
       </c>
       <c r="Q218" t="n">
         <v>0</v>
       </c>
       <c r="R218" t="n">
-        <v>46146020.12</v>
+        <v>0</v>
       </c>
       <c r="S218" t="n">
-        <v>38990514.67</v>
+        <v>0</v>
       </c>
       <c r="T218" t="n">
-        <v>40603278.83</v>
+        <v>0</v>
       </c>
       <c r="U218" t="n">
-        <v>39757673.56</v>
+        <v>0</v>
       </c>
       <c r="V218" t="n">
-        <v>1612764.16</v>
+        <v>0</v>
       </c>
       <c r="W218" t="n">
-        <v>61292510</v>
+        <v>0</v>
       </c>
       <c r="X218" t="n">
-        <v>61292510</v>
+        <v>0</v>
       </c>
       <c r="Y218" t="n">
         <v>0</v>
@@ -30936,7 +30936,7 @@
         <v>0</v>
       </c>
       <c r="AA218" t="n">
-        <v>61292510</v>
+        <v>0</v>
       </c>
       <c r="AB218" t="n">
         <v>5</v>
@@ -30954,27 +30954,167 @@
       </c>
       <c r="AF218" t="inlineStr">
         <is>
+          <t>00 - Tesouro Municipal</t>
+        </is>
+      </c>
+      <c r="AG218" t="inlineStr">
+        <is>
+          <t>Contratação PJ sem Fins Lucrativos</t>
+        </is>
+      </c>
+      <c r="AH218" t="inlineStr">
+        <is>
+          <t>Recursos do FUMCAD desvinculados</t>
+        </is>
+      </c>
+      <c r="AI218" t="inlineStr">
+        <is>
+          <t>90.10.14.422.4019.6160.33503900.00.1.501.0004</t>
+        </is>
+      </c>
+      <c r="AJ218" t="inlineStr">
+        <is>
+          <t>11/08/2026 07:13:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E219" t="n">
+        <v>422</v>
+      </c>
+      <c r="F219" t="n">
+        <v>4019</v>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>6160</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>33503900</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>0958</t>
+        </is>
+      </c>
+      <c r="L219" t="n">
+        <v>34621230.63</v>
+      </c>
+      <c r="M219" t="n">
+        <v>0</v>
+      </c>
+      <c r="N219" t="n">
+        <v>0</v>
+      </c>
+      <c r="O219" t="n">
+        <v>33234725.6</v>
+      </c>
+      <c r="P219" t="n">
+        <v>6388346.56</v>
+      </c>
+      <c r="Q219" t="n">
+        <v>0</v>
+      </c>
+      <c r="R219" t="n">
+        <v>46146020.12</v>
+      </c>
+      <c r="S219" t="n">
+        <v>38990514.67</v>
+      </c>
+      <c r="T219" t="n">
+        <v>40603278.83</v>
+      </c>
+      <c r="U219" t="n">
+        <v>39757673.56</v>
+      </c>
+      <c r="V219" t="n">
+        <v>1612764.16</v>
+      </c>
+      <c r="W219" t="n">
+        <v>61292510</v>
+      </c>
+      <c r="X219" t="n">
+        <v>61292510</v>
+      </c>
+      <c r="Y219" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z219" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA219" t="n">
+        <v>61292510</v>
+      </c>
+      <c r="AB219" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC219" t="inlineStr"/>
+      <c r="AD219" t="inlineStr">
+        <is>
+          <t>Criança e Adolescente</t>
+        </is>
+      </c>
+      <c r="AE219" t="inlineStr">
+        <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="AF219" t="inlineStr">
+        <is>
           <t>08 - Recusos Vinculados</t>
         </is>
       </c>
-      <c r="AG218" t="inlineStr">
+      <c r="AG219" t="inlineStr">
         <is>
           <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
-      <c r="AH218" t="inlineStr">
+      <c r="AH219" t="inlineStr">
         <is>
           <t>PMSP-SMDHC/FUMCAD</t>
         </is>
       </c>
-      <c r="AI218" t="inlineStr">
+      <c r="AI219" t="inlineStr">
         <is>
           <t>90.10.14.422.4019.6160.33503900.08.1.759.0958</t>
         </is>
       </c>
-      <c r="AJ218" t="inlineStr">
-        <is>
-          <t>10/08/2026 07:34:19</t>
+      <c r="AJ219" t="inlineStr">
+        <is>
+          <t>11/08/2026 07:13:07</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202608.xlsx
+++ b/base_despesas/2026/despesas_202608.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>117046.33</v>
+        <v>118327.6</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4424061.02</v>
+        <v>4424088.37</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>4008203.67</v>
+        <v>4154942.18</v>
       </c>
       <c r="P10" t="n">
         <v>7381353.64</v>
@@ -1789,7 +1789,7 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>19021569.48</v>
+        <v>19022872.6</v>
       </c>
       <c r="S10" t="n">
         <v>8779487.99</v>
@@ -1798,7 +1798,7 @@
         <v>9694004.050000001</v>
       </c>
       <c r="U10" t="n">
-        <v>11640215.84</v>
+        <v>11641518.96</v>
       </c>
       <c r="V10" t="n">
         <v>914516.0600000001</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>879668.34</v>
+        <v>1028688.4</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -4571,7 +4571,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1122562.34</v>
+        <v>1142642.78</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>8307446.77</v>
+        <v>8575351.300000001</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -4860,16 +4860,16 @@
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>8104580.11</v>
+        <v>8259564.78</v>
       </c>
       <c r="P32" t="n">
-        <v>5620655.33</v>
+        <v>5647047.17</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>23382056.17</v>
+        <v>23401872.01</v>
       </c>
       <c r="S32" t="n">
         <v>17034593.44</v>
@@ -4878,7 +4878,7 @@
         <v>20548620.15</v>
       </c>
       <c r="U32" t="n">
-        <v>17761400.84</v>
+        <v>17754824.84</v>
       </c>
       <c r="V32" t="n">
         <v>3514026.71</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -4991,7 +4991,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>384774.54</v>
+        <v>414058.49</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1636075.63</v>
+        <v>1636725.56</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -6540,7 +6540,7 @@
         <v>1006324.68</v>
       </c>
       <c r="O44" t="n">
-        <v>587219.74</v>
+        <v>706433.0600000001</v>
       </c>
       <c r="P44" t="n">
         <v>1392117.74</v>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -6680,7 +6680,7 @@
         <v>93886</v>
       </c>
       <c r="O45" t="n">
-        <v>2447815.85</v>
+        <v>2461407.33</v>
       </c>
       <c r="P45" t="n">
         <v>16620776.87</v>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -8491,7 +8491,7 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>6600922.5</v>
+        <v>8643538.5</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -11589,7 +11589,7 @@
         <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -11598,7 +11598,7 @@
         <v>0</v>
       </c>
       <c r="U80" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="V80" t="n">
         <v>0</v>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -12000,7 +12000,7 @@
         <v>0</v>
       </c>
       <c r="O83" t="n">
-        <v>680791.95</v>
+        <v>1191556.45</v>
       </c>
       <c r="P83" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -14240,7 +14240,7 @@
         <v>0</v>
       </c>
       <c r="O99" t="n">
-        <v>77549.86</v>
+        <v>97826.36</v>
       </c>
       <c r="P99" t="n">
         <v>110020.45</v>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -17749,7 +17749,7 @@
         <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>0</v>
+        <v>130000</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -17758,7 +17758,7 @@
         <v>0</v>
       </c>
       <c r="U124" t="n">
-        <v>0</v>
+        <v>130000</v>
       </c>
       <c r="V124" t="n">
         <v>0</v>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -19143,7 +19143,7 @@
         <v>9429.48</v>
       </c>
       <c r="P134" t="n">
-        <v>8373</v>
+        <v>9541.52</v>
       </c>
       <c r="Q134" t="n">
         <v>2225</v>
@@ -19152,16 +19152,16 @@
         <v>18971</v>
       </c>
       <c r="S134" t="n">
-        <v>10598</v>
+        <v>9429.48</v>
       </c>
       <c r="T134" t="n">
         <v>10598</v>
       </c>
       <c r="U134" t="n">
-        <v>10598</v>
+        <v>9429.48</v>
       </c>
       <c r="V134" t="n">
-        <v>0</v>
+        <v>1168.52</v>
       </c>
       <c r="W134" t="n">
         <v>10598</v>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -20820,7 +20820,7 @@
         <v>0</v>
       </c>
       <c r="O146" t="n">
-        <v>979135.6899999999</v>
+        <v>1223562.31</v>
       </c>
       <c r="P146" t="n">
         <v>15454293.91</v>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -21520,7 +21520,7 @@
         <v>190000</v>
       </c>
       <c r="O151" t="n">
-        <v>161916.85</v>
+        <v>202787.33</v>
       </c>
       <c r="P151" t="n">
         <v>348711.89</v>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -22211,7 +22211,7 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>46763.29</v>
+        <v>74047.78999999999</v>
       </c>
       <c r="M156" t="n">
         <v>0</v>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -25860,7 +25860,7 @@
         <v>0</v>
       </c>
       <c r="O182" t="n">
-        <v>620095.8199999999</v>
+        <v>649805.4300000001</v>
       </c>
       <c r="P182" t="n">
         <v>1473088.82</v>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -27960,7 +27960,7 @@
         <v>0</v>
       </c>
       <c r="O197" t="n">
-        <v>10200</v>
+        <v>10800</v>
       </c>
       <c r="P197" t="n">
         <v>11400</v>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -29512,10 +29512,10 @@
         <v>214390827.19</v>
       </c>
       <c r="S208" t="n">
-        <v>153077170.3</v>
+        <v>154173329.55</v>
       </c>
       <c r="T208" t="n">
-        <v>158744546.54</v>
+        <v>159840705.79</v>
       </c>
       <c r="U208" t="n">
         <v>164582306.15</v>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>
@@ -31031,7 +31031,7 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>34621230.63</v>
+        <v>34814362.52</v>
       </c>
       <c r="M219" t="n">
         <v>0</v>
@@ -31040,7 +31040,7 @@
         <v>0</v>
       </c>
       <c r="O219" t="n">
-        <v>33234725.6</v>
+        <v>34339454.49</v>
       </c>
       <c r="P219" t="n">
         <v>6388346.56</v>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>11/08/2026 07:13:07</t>
+          <t>12/08/2026 09:48:18</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202608.xlsx
+++ b/base_despesas/2026/despesas_202608.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
         <v>334134</v>
       </c>
       <c r="O7" t="n">
-        <v>152052.25</v>
+        <v>157380.45</v>
       </c>
       <c r="P7" t="n">
         <v>308127.99</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>118327.6</v>
+        <v>118595.35</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>4154942.18</v>
+        <v>4164060.74</v>
       </c>
       <c r="P10" t="n">
         <v>7381353.64</v>
@@ -1789,16 +1789,16 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>19022872.6</v>
+        <v>19023831.4</v>
       </c>
       <c r="S10" t="n">
-        <v>8779487.99</v>
+        <v>8780791.109999999</v>
       </c>
       <c r="T10" t="n">
-        <v>9694004.050000001</v>
+        <v>9695307.17</v>
       </c>
       <c r="U10" t="n">
-        <v>11641518.96</v>
+        <v>11642477.76</v>
       </c>
       <c r="V10" t="n">
         <v>914516.0600000001</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -2760,7 +2760,7 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>5459</v>
+        <v>69900.72</v>
       </c>
       <c r="P17" t="n">
         <v>10008.92</v>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2962311.1</v>
+        <v>2968071.1</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>8575351.300000001</v>
+        <v>8666240.039999999</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -5420,7 +5420,7 @@
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>1636075.63</v>
+        <v>1636725.56</v>
       </c>
       <c r="P36" t="n">
         <v>2931914.44</v>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>9985.280000000001</v>
+        <v>10313.28</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -6671,7 +6671,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2510025.21</v>
+        <v>2520769.82</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -11431,7 +11431,7 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>80000</v>
       </c>
       <c r="M79" t="n">
         <v>0</v>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -20811,7 +20811,7 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>1282362.31</v>
+        <v>1283862.31</v>
       </c>
       <c r="M146" t="n">
         <v>0</v>
@@ -20820,7 +20820,7 @@
         <v>0</v>
       </c>
       <c r="O146" t="n">
-        <v>1223562.31</v>
+        <v>1224562.31</v>
       </c>
       <c r="P146" t="n">
         <v>15454293.91</v>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -29491,7 +29491,7 @@
         </is>
       </c>
       <c r="L208" t="n">
-        <v>118180673.01</v>
+        <v>120257278.47</v>
       </c>
       <c r="M208" t="n">
         <v>0</v>
@@ -29500,7 +29500,7 @@
         <v>0</v>
       </c>
       <c r="O208" t="n">
-        <v>117374145.55</v>
+        <v>118054416.06</v>
       </c>
       <c r="P208" t="n">
         <v>49808521.04</v>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -29920,7 +29920,7 @@
         <v>0</v>
       </c>
       <c r="O211" t="n">
-        <v>60344741.71</v>
+        <v>62273213.71</v>
       </c>
       <c r="P211" t="n">
         <v>62818272</v>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -30051,7 +30051,7 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>47775619.8</v>
+        <v>48765619.8</v>
       </c>
       <c r="M212" t="n">
         <v>0</v>
@@ -30060,7 +30060,7 @@
         <v>0</v>
       </c>
       <c r="O212" t="n">
-        <v>47261773.84</v>
+        <v>47381410.28</v>
       </c>
       <c r="P212" t="n">
         <v>50438263.91</v>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>
@@ -31031,7 +31031,7 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>34814362.52</v>
+        <v>34876296.58</v>
       </c>
       <c r="M219" t="n">
         <v>0</v>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>12/08/2026 09:48:18</t>
+          <t>13/08/2026 07:24:37</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202608.xlsx
+++ b/base_despesas/2026/despesas_202608.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -1792,10 +1792,10 @@
         <v>19023831.4</v>
       </c>
       <c r="S10" t="n">
-        <v>8780791.109999999</v>
+        <v>8786024.300000001</v>
       </c>
       <c r="T10" t="n">
-        <v>9695307.17</v>
+        <v>9700540.359999999</v>
       </c>
       <c r="U10" t="n">
         <v>11642477.76</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -12420,7 +12420,7 @@
         <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>861800</v>
+        <v>993550</v>
       </c>
       <c r="P86" t="n">
         <v>0</v>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -14380,7 +14380,7 @@
         <v>40000</v>
       </c>
       <c r="O100" t="n">
-        <v>5442.34</v>
+        <v>5467.34</v>
       </c>
       <c r="P100" t="n">
         <v>450</v>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -15911,7 +15911,7 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>90000</v>
       </c>
       <c r="M111" t="n">
         <v>0</v>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -19420,7 +19420,7 @@
         <v>0</v>
       </c>
       <c r="O136" t="n">
-        <v>6276033.41</v>
+        <v>6282898.35</v>
       </c>
       <c r="P136" t="n">
         <v>0</v>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -20811,7 +20811,7 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>1283862.31</v>
+        <v>1286362.31</v>
       </c>
       <c r="M146" t="n">
         <v>0</v>
@@ -20820,7 +20820,7 @@
         <v>0</v>
       </c>
       <c r="O146" t="n">
-        <v>1224562.31</v>
+        <v>1226062.31</v>
       </c>
       <c r="P146" t="n">
         <v>15454293.91</v>
@@ -20832,10 +20832,10 @@
         <v>23880736.73</v>
       </c>
       <c r="S146" t="n">
-        <v>2668440.26</v>
+        <v>2716328.85</v>
       </c>
       <c r="T146" t="n">
-        <v>2679440.26</v>
+        <v>2727328.85</v>
       </c>
       <c r="U146" t="n">
         <v>8426442.82</v>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -21660,7 +21660,7 @@
         <v>50000</v>
       </c>
       <c r="O152" t="n">
-        <v>24782.24</v>
+        <v>24857.24</v>
       </c>
       <c r="P152" t="n">
         <v>2250</v>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -22500,7 +22500,7 @@
         <v>211572</v>
       </c>
       <c r="O158" t="n">
-        <v>1499977.67</v>
+        <v>1517019.68</v>
       </c>
       <c r="P158" t="n">
         <v>2681423.67</v>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -26000,7 +26000,7 @@
         <v>0</v>
       </c>
       <c r="O183" t="n">
-        <v>1445805.7</v>
+        <v>1465931.48</v>
       </c>
       <c r="P183" t="n">
         <v>1825657.74</v>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -27680,7 +27680,7 @@
         <v>0</v>
       </c>
       <c r="O195" t="n">
-        <v>191.92</v>
+        <v>266.92</v>
       </c>
       <c r="P195" t="n">
         <v>925</v>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -29500,7 +29500,7 @@
         <v>0</v>
       </c>
       <c r="O208" t="n">
-        <v>118054416.06</v>
+        <v>118161204.58</v>
       </c>
       <c r="P208" t="n">
         <v>49808521.04</v>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -30051,7 +30051,7 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>48765619.8</v>
+        <v>48945619.8</v>
       </c>
       <c r="M212" t="n">
         <v>0</v>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>
@@ -31049,7 +31049,7 @@
         <v>0</v>
       </c>
       <c r="R219" t="n">
-        <v>46146020.12</v>
+        <v>46866871.52</v>
       </c>
       <c r="S219" t="n">
         <v>38990514.67</v>
@@ -31058,7 +31058,7 @@
         <v>40603278.83</v>
       </c>
       <c r="U219" t="n">
-        <v>39757673.56</v>
+        <v>40478524.96</v>
       </c>
       <c r="V219" t="n">
         <v>1612764.16</v>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>13/08/2026 07:24:37</t>
+          <t>14/08/2026 15:32:17</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202608.xlsx
+++ b/base_despesas/2026/despesas_202608.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -1360,16 +1360,16 @@
         <v>334134</v>
       </c>
       <c r="O7" t="n">
-        <v>157380.45</v>
+        <v>161853.45</v>
       </c>
       <c r="P7" t="n">
-        <v>308127.99</v>
+        <v>370240.19</v>
       </c>
       <c r="Q7" t="n">
         <v>63262</v>
       </c>
       <c r="R7" t="n">
-        <v>963658.64</v>
+        <v>1032083.64</v>
       </c>
       <c r="S7" t="n">
         <v>308328.21</v>
@@ -1378,7 +1378,7 @@
         <v>413328.21</v>
       </c>
       <c r="U7" t="n">
-        <v>655530.65</v>
+        <v>661843.45</v>
       </c>
       <c r="V7" t="n">
         <v>105000</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1640,7 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>143525.85</v>
+        <v>172231.02</v>
       </c>
       <c r="P9" t="n">
         <v>332289.52</v>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4424088.37</v>
+        <v>4438158.98</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1780,28 +1780,28 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>4164060.74</v>
+        <v>4200361.21</v>
       </c>
       <c r="P10" t="n">
-        <v>7381353.64</v>
+        <v>7382808.04</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>19023831.4</v>
+        <v>19028327.66</v>
       </c>
       <c r="S10" t="n">
-        <v>8786024.300000001</v>
+        <v>8788091.76</v>
       </c>
       <c r="T10" t="n">
-        <v>9700540.359999999</v>
+        <v>9703566.619999999</v>
       </c>
       <c r="U10" t="n">
-        <v>11642477.76</v>
+        <v>11645519.62</v>
       </c>
       <c r="V10" t="n">
-        <v>914516.0600000001</v>
+        <v>915474.86</v>
       </c>
       <c r="W10" t="n">
         <v>11656658.15</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>145749.76</v>
+        <v>146554.62</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>879668.34</v>
+        <v>1028688.4</v>
       </c>
       <c r="P18" t="n">
         <v>26813.15</v>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2968071.1</v>
+        <v>2969237.76</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
         <v>50000</v>
       </c>
       <c r="R24" t="n">
-        <v>75842.42</v>
+        <v>85353.67999999999</v>
       </c>
       <c r="S24" t="n">
         <v>6040.6</v>
@@ -3758,7 +3758,7 @@
         <v>6040.6</v>
       </c>
       <c r="U24" t="n">
-        <v>7378.36</v>
+        <v>16889.62</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -4303,13 +4303,13 @@
         <v>121474.12</v>
       </c>
       <c r="P28" t="n">
-        <v>137870.4</v>
+        <v>141816.38</v>
       </c>
       <c r="Q28" t="n">
         <v>2308</v>
       </c>
       <c r="R28" t="n">
-        <v>757054.3199999999</v>
+        <v>805054.3199999999</v>
       </c>
       <c r="S28" t="n">
         <v>481844.58</v>
@@ -4318,7 +4318,7 @@
         <v>481844.58</v>
       </c>
       <c r="U28" t="n">
-        <v>619183.92</v>
+        <v>663237.9399999999</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>982211.52</v>
+        <v>986234.11</v>
       </c>
       <c r="P30" t="n">
         <v>614271.01</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -4720,7 +4720,7 @@
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>2243756</v>
+        <v>2692507.2</v>
       </c>
       <c r="P31" t="n">
         <v>6144274.42</v>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>8666240.039999999</v>
+        <v>8666739.74</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -6403,13 +6403,13 @@
         <v>8172.88</v>
       </c>
       <c r="P43" t="n">
-        <v>67000</v>
+        <v>68092.11</v>
       </c>
       <c r="Q43" t="n">
         <v>22671</v>
       </c>
       <c r="R43" t="n">
-        <v>213197.34</v>
+        <v>260197.34</v>
       </c>
       <c r="S43" t="n">
         <v>51657</v>
@@ -6418,7 +6418,7 @@
         <v>55593</v>
       </c>
       <c r="U43" t="n">
-        <v>146197.34</v>
+        <v>192105.23</v>
       </c>
       <c r="V43" t="n">
         <v>3936</v>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -6671,7 +6671,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2520769.82</v>
+        <v>2523214.16</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -6680,7 +6680,7 @@
         <v>93886</v>
       </c>
       <c r="O45" t="n">
-        <v>2461407.33</v>
+        <v>2473531.67</v>
       </c>
       <c r="P45" t="n">
         <v>16620776.87</v>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -7532,10 +7532,10 @@
         <v>13632475.23</v>
       </c>
       <c r="S51" t="n">
-        <v>9024683</v>
+        <v>9291804.449999999</v>
       </c>
       <c r="T51" t="n">
-        <v>11429605.99</v>
+        <v>11696727.44</v>
       </c>
       <c r="U51" t="n">
         <v>9291804.449999999</v>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7660,7 @@
         <v>217009.89</v>
       </c>
       <c r="O52" t="n">
-        <v>110894.5</v>
+        <v>133073.4</v>
       </c>
       <c r="P52" t="n">
         <v>93205.11</v>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -11869,7 +11869,7 @@
         <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>107000</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -11878,7 +11878,7 @@
         <v>0</v>
       </c>
       <c r="U82" t="n">
-        <v>0</v>
+        <v>107000</v>
       </c>
       <c r="V82" t="n">
         <v>0</v>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -13963,13 +13963,13 @@
         <v>9750.41</v>
       </c>
       <c r="P97" t="n">
-        <v>1124.65</v>
+        <v>1235.82</v>
       </c>
       <c r="Q97" t="n">
         <v>30045</v>
       </c>
       <c r="R97" t="n">
-        <v>77358.83</v>
+        <v>93241.23</v>
       </c>
       <c r="S97" t="n">
         <v>76123.00999999999</v>
@@ -13978,7 +13978,7 @@
         <v>76123.00999999999</v>
       </c>
       <c r="U97" t="n">
-        <v>76234.17999999999</v>
+        <v>92005.41</v>
       </c>
       <c r="V97" t="n">
         <v>0</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -14100,7 +14100,7 @@
         <v>0</v>
       </c>
       <c r="O98" t="n">
-        <v>204807.15</v>
+        <v>214716.19</v>
       </c>
       <c r="P98" t="n">
         <v>115327.53</v>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -14243,7 +14243,7 @@
         <v>97826.36</v>
       </c>
       <c r="P99" t="n">
-        <v>110020.45</v>
+        <v>260020.45</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
@@ -14258,7 +14258,7 @@
         <v>141543.91</v>
       </c>
       <c r="U99" t="n">
-        <v>430094.85</v>
+        <v>280094.85</v>
       </c>
       <c r="V99" t="n">
         <v>1350</v>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -15220,7 +15220,7 @@
         <v>72910.97</v>
       </c>
       <c r="O106" t="n">
-        <v>32631.35</v>
+        <v>39157.62</v>
       </c>
       <c r="P106" t="n">
         <v>84798.03</v>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -18863,7 +18863,7 @@
         <v>0</v>
       </c>
       <c r="P132" t="n">
-        <v>2117.1</v>
+        <v>3154.2</v>
       </c>
       <c r="Q132" t="n">
         <v>0</v>
@@ -18878,7 +18878,7 @@
         <v>31080</v>
       </c>
       <c r="U132" t="n">
-        <v>50000</v>
+        <v>48962.9</v>
       </c>
       <c r="V132" t="n">
         <v>0</v>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -20683,13 +20683,13 @@
         <v>0</v>
       </c>
       <c r="P145" t="n">
-        <v>0</v>
+        <v>19046</v>
       </c>
       <c r="Q145" t="n">
         <v>0</v>
       </c>
       <c r="R145" t="n">
-        <v>19646</v>
+        <v>39246</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -20698,7 +20698,7 @@
         <v>0</v>
       </c>
       <c r="U145" t="n">
-        <v>19646</v>
+        <v>20200</v>
       </c>
       <c r="V145" t="n">
         <v>0</v>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -20811,7 +20811,7 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>1286362.31</v>
+        <v>1290362.31</v>
       </c>
       <c r="M146" t="n">
         <v>0</v>
@@ -20820,7 +20820,7 @@
         <v>0</v>
       </c>
       <c r="O146" t="n">
-        <v>1226062.31</v>
+        <v>1265262.31</v>
       </c>
       <c r="P146" t="n">
         <v>15454293.91</v>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -21100,7 +21100,7 @@
         <v>0</v>
       </c>
       <c r="O148" t="n">
-        <v>32631.35</v>
+        <v>39157.62</v>
       </c>
       <c r="P148" t="n">
         <v>0</v>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -21249,7 +21249,7 @@
         <v>0</v>
       </c>
       <c r="R149" t="n">
-        <v>87627.35000000001</v>
+        <v>107627.35</v>
       </c>
       <c r="S149" t="n">
         <v>16605</v>
@@ -21258,7 +21258,7 @@
         <v>16605</v>
       </c>
       <c r="U149" t="n">
-        <v>87627.35000000001</v>
+        <v>107627.35</v>
       </c>
       <c r="V149" t="n">
         <v>0</v>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -21380,7 +21380,7 @@
         <v>234940.86</v>
       </c>
       <c r="O150" t="n">
-        <v>143525.85</v>
+        <v>172231.02</v>
       </c>
       <c r="P150" t="n">
         <v>118643.14</v>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -21651,7 +21651,7 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>24904.11</v>
+        <v>25058.24</v>
       </c>
       <c r="M152" t="n">
         <v>0</v>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -22223,13 +22223,13 @@
         <v>46435.29</v>
       </c>
       <c r="P156" t="n">
-        <v>649248.8199999999</v>
+        <v>679875.02</v>
       </c>
       <c r="Q156" t="n">
         <v>8077</v>
       </c>
       <c r="R156" t="n">
-        <v>1018879.14</v>
+        <v>1038879.14</v>
       </c>
       <c r="S156" t="n">
         <v>175845.16</v>
@@ -22238,7 +22238,7 @@
         <v>175845.16</v>
       </c>
       <c r="U156" t="n">
-        <v>369630.32</v>
+        <v>359004.12</v>
       </c>
       <c r="V156" t="n">
         <v>0</v>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -22491,7 +22491,7 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>1554642.66</v>
+        <v>1556687.74</v>
       </c>
       <c r="M158" t="n">
         <v>0</v>
@@ -22500,7 +22500,7 @@
         <v>211572</v>
       </c>
       <c r="O158" t="n">
-        <v>1517019.68</v>
+        <v>1537477.76</v>
       </c>
       <c r="P158" t="n">
         <v>2681423.67</v>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -23632,10 +23632,10 @@
         <v>60000</v>
       </c>
       <c r="S166" t="n">
-        <v>0</v>
+        <v>60000</v>
       </c>
       <c r="T166" t="n">
-        <v>0</v>
+        <v>60000</v>
       </c>
       <c r="U166" t="n">
         <v>60000</v>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -25583,13 +25583,13 @@
         <v>82853.60000000001</v>
       </c>
       <c r="P180" t="n">
-        <v>7647.82</v>
+        <v>46171.82</v>
       </c>
       <c r="Q180" t="n">
         <v>0</v>
       </c>
       <c r="R180" t="n">
-        <v>228416.15</v>
+        <v>267909.15</v>
       </c>
       <c r="S180" t="n">
         <v>160506.12</v>
@@ -25598,7 +25598,7 @@
         <v>162300.12</v>
       </c>
       <c r="U180" t="n">
-        <v>220768.33</v>
+        <v>221737.33</v>
       </c>
       <c r="V180" t="n">
         <v>1794</v>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -25860,7 +25860,7 @@
         <v>0</v>
       </c>
       <c r="O182" t="n">
-        <v>649805.4300000001</v>
+        <v>744555.9399999999</v>
       </c>
       <c r="P182" t="n">
         <v>1473088.82</v>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -26003,7 +26003,7 @@
         <v>1465931.48</v>
       </c>
       <c r="P183" t="n">
-        <v>1825657.74</v>
+        <v>2232586.71</v>
       </c>
       <c r="Q183" t="n">
         <v>0</v>
@@ -26018,7 +26018,7 @@
         <v>2507776.98</v>
       </c>
       <c r="U183" t="n">
-        <v>3692184.08</v>
+        <v>3285255.11</v>
       </c>
       <c r="V183" t="n">
         <v>104347.76</v>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -29086,7 +29086,7 @@
         <v>0</v>
       </c>
       <c r="Q205" t="n">
-        <v>0</v>
+        <v>600000</v>
       </c>
       <c r="R205" t="n">
         <v>0</v>
@@ -29104,7 +29104,7 @@
         <v>0</v>
       </c>
       <c r="W205" t="n">
-        <v>600437</v>
+        <v>1200437</v>
       </c>
       <c r="X205" t="n">
         <v>16896102</v>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -29491,7 +29491,7 @@
         </is>
       </c>
       <c r="L208" t="n">
-        <v>120257278.47</v>
+        <v>120276734.86</v>
       </c>
       <c r="M208" t="n">
         <v>0</v>
@@ -29512,10 +29512,10 @@
         <v>214390827.19</v>
       </c>
       <c r="S208" t="n">
-        <v>154173329.55</v>
+        <v>157461807.3</v>
       </c>
       <c r="T208" t="n">
-        <v>159840705.79</v>
+        <v>163129183.54</v>
       </c>
       <c r="U208" t="n">
         <v>164582306.15</v>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -29911,7 +29911,7 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>62273213.71</v>
+        <v>64701463.71</v>
       </c>
       <c r="M211" t="n">
         <v>0</v>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -30051,7 +30051,7 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>48945619.8</v>
+        <v>52542619.8</v>
       </c>
       <c r="M212" t="n">
         <v>0</v>
@@ -30060,7 +30060,7 @@
         <v>0</v>
       </c>
       <c r="O212" t="n">
-        <v>47381410.28</v>
+        <v>47471410.28</v>
       </c>
       <c r="P212" t="n">
         <v>50438263.91</v>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>
@@ -31049,7 +31049,7 @@
         <v>0</v>
       </c>
       <c r="R219" t="n">
-        <v>46866871.52</v>
+        <v>47237841.52</v>
       </c>
       <c r="S219" t="n">
         <v>38990514.67</v>
@@ -31058,7 +31058,7 @@
         <v>40603278.83</v>
       </c>
       <c r="U219" t="n">
-        <v>40478524.96</v>
+        <v>40849494.96</v>
       </c>
       <c r="V219" t="n">
         <v>1612764.16</v>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>14/08/2026 15:32:17</t>
+          <t>15/08/2026 06:39:44</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202608.xlsx
+++ b/base_despesas/2026/despesas_202608.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -14249,16 +14249,16 @@
         <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>540115.3</v>
+        <v>540236.66</v>
       </c>
       <c r="S99" t="n">
-        <v>140193.91</v>
+        <v>140315.27</v>
       </c>
       <c r="T99" t="n">
-        <v>141543.91</v>
+        <v>141665.27</v>
       </c>
       <c r="U99" t="n">
-        <v>280094.85</v>
+        <v>280216.21</v>
       </c>
       <c r="V99" t="n">
         <v>1350</v>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -21529,16 +21529,16 @@
         <v>0</v>
       </c>
       <c r="R151" t="n">
-        <v>774473.36</v>
+        <v>774707.3</v>
       </c>
       <c r="S151" t="n">
-        <v>293818.07</v>
+        <v>294052.01</v>
       </c>
       <c r="T151" t="n">
-        <v>377547.69</v>
+        <v>377781.63</v>
       </c>
       <c r="U151" t="n">
-        <v>425761.47</v>
+        <v>425995.41</v>
       </c>
       <c r="V151" t="n">
         <v>83729.62</v>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -22509,16 +22509,16 @@
         <v>324976</v>
       </c>
       <c r="R158" t="n">
-        <v>6629608.39</v>
+        <v>6629661.87</v>
       </c>
       <c r="S158" t="n">
-        <v>2726699.82</v>
+        <v>2726753.3</v>
       </c>
       <c r="T158" t="n">
-        <v>2727019.82</v>
+        <v>2727073.3</v>
       </c>
       <c r="U158" t="n">
-        <v>3948184.72</v>
+        <v>3948238.2</v>
       </c>
       <c r="V158" t="n">
         <v>320</v>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>15/08/2026 06:39:44</t>
+          <t>17/08/2026 06:57:59</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202608.xlsx
+++ b/base_despesas/2026/despesas_202608.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>128086</v>
+        <v>93886</v>
       </c>
       <c r="X4" t="n">
         <v>50000</v>
@@ -973,10 +973,10 @@
         <v>50000</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>34200</v>
       </c>
       <c r="AA4" t="n">
-        <v>178086</v>
+        <v>143886</v>
       </c>
       <c r="AB4" t="n">
         <v>5</v>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4438158.98</v>
+        <v>4614723.6</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>146554.62</v>
+        <v>140887.93</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1935,13 +1935,13 @@
         <v>568286.11</v>
       </c>
       <c r="T11" t="n">
-        <v>568736.11</v>
+        <v>650222.22</v>
       </c>
       <c r="U11" t="n">
         <v>568286.11</v>
       </c>
       <c r="V11" t="n">
-        <v>450</v>
+        <v>81936.11</v>
       </c>
       <c r="W11" t="n">
         <v>569098</v>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -4583,13 +4583,13 @@
         <v>986234.11</v>
       </c>
       <c r="P30" t="n">
-        <v>614271.01</v>
+        <v>641271.01</v>
       </c>
       <c r="Q30" t="n">
         <v>9180</v>
       </c>
       <c r="R30" t="n">
-        <v>2456007.01</v>
+        <v>2482383.88</v>
       </c>
       <c r="S30" t="n">
         <v>1718528.16</v>
@@ -4598,7 +4598,7 @@
         <v>1875118.94</v>
       </c>
       <c r="U30" t="n">
-        <v>1841736</v>
+        <v>1841112.87</v>
       </c>
       <c r="V30" t="n">
         <v>156590.78</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>8666739.74</v>
+        <v>9413730.609999999</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -6671,7 +6671,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2523214.16</v>
+        <v>2624273.45</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -6689,16 +6689,16 @@
         <v>1186346</v>
       </c>
       <c r="R45" t="n">
-        <v>31073365.83</v>
+        <v>31076878.03</v>
       </c>
       <c r="S45" t="n">
-        <v>5302391.8</v>
+        <v>5305904</v>
       </c>
       <c r="T45" t="n">
-        <v>5735668.95</v>
+        <v>5739181.15</v>
       </c>
       <c r="U45" t="n">
-        <v>14452588.96</v>
+        <v>14456101.16</v>
       </c>
       <c r="V45" t="n">
         <v>433277.15</v>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -14937,7 +14937,7 @@
         <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>75499.36</v>
+        <v>83548.96000000001</v>
       </c>
       <c r="O104" t="n">
         <v>1690301.29</v>
@@ -14964,7 +14964,7 @@
         <v>0</v>
       </c>
       <c r="W104" t="n">
-        <v>2182531.36</v>
+        <v>2190580.96</v>
       </c>
       <c r="X104" t="n">
         <v>2107032</v>
@@ -14976,7 +14976,7 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>2182531.36</v>
+        <v>2190580.96</v>
       </c>
       <c r="AB104" t="n">
         <v>5</v>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -15104,7 +15104,7 @@
         <v>0</v>
       </c>
       <c r="W105" t="n">
-        <v>69823</v>
+        <v>61773.4</v>
       </c>
       <c r="X105" t="n">
         <v>80000</v>
@@ -15113,10 +15113,10 @@
         <v>10177</v>
       </c>
       <c r="Z105" t="n">
-        <v>0</v>
+        <v>8049.6</v>
       </c>
       <c r="AA105" t="n">
-        <v>80000</v>
+        <v>71950.39999999999</v>
       </c>
       <c r="AB105" t="n">
         <v>5</v>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -15491,7 +15491,7 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>60000</v>
       </c>
       <c r="M108" t="n">
         <v>0</v>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -17311,7 +17311,7 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>400000</v>
+        <v>470000</v>
       </c>
       <c r="M121" t="n">
         <v>0</v>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -19411,7 +19411,7 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>6282898.35</v>
+        <v>7195593.68</v>
       </c>
       <c r="M136" t="n">
         <v>0</v>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -20811,7 +20811,7 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>1290362.31</v>
+        <v>1296362.31</v>
       </c>
       <c r="M146" t="n">
         <v>0</v>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -22244,7 +22244,7 @@
         <v>0</v>
       </c>
       <c r="W156" t="n">
-        <v>418094</v>
+        <v>374541</v>
       </c>
       <c r="X156" t="n">
         <v>158832</v>
@@ -22253,10 +22253,10 @@
         <v>8077</v>
       </c>
       <c r="Z156" t="n">
-        <v>0</v>
+        <v>43553</v>
       </c>
       <c r="AA156" t="n">
-        <v>418094</v>
+        <v>374541</v>
       </c>
       <c r="AB156" t="n">
         <v>5</v>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -24749,7 +24749,7 @@
         <v>0</v>
       </c>
       <c r="R174" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="S174" t="n">
         <v>0</v>
@@ -24758,7 +24758,7 @@
         <v>0</v>
       </c>
       <c r="U174" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="V174" t="n">
         <v>0</v>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -28097,7 +28097,7 @@
         <v>0</v>
       </c>
       <c r="N198" t="n">
-        <v>0</v>
+        <v>77753</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
@@ -28124,7 +28124,7 @@
         <v>0</v>
       </c>
       <c r="W198" t="n">
-        <v>33669</v>
+        <v>111422</v>
       </c>
       <c r="X198" t="n">
         <v>220966</v>
@@ -28136,7 +28136,7 @@
         <v>0</v>
       </c>
       <c r="AA198" t="n">
-        <v>220966</v>
+        <v>298719</v>
       </c>
       <c r="AB198" t="n">
         <v>5</v>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -29512,10 +29512,10 @@
         <v>214390827.19</v>
       </c>
       <c r="S208" t="n">
-        <v>157461807.3</v>
+        <v>158557966.55</v>
       </c>
       <c r="T208" t="n">
-        <v>163129183.54</v>
+        <v>164225342.79</v>
       </c>
       <c r="U208" t="n">
         <v>164582306.15</v>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>
@@ -31031,7 +31031,7 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>34876296.58</v>
+        <v>35122742.46</v>
       </c>
       <c r="M219" t="n">
         <v>0</v>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>17/08/2026 06:57:59</t>
+          <t>18/08/2026 06:52:34</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202608.xlsx
+++ b/base_despesas/2026/despesas_202608.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
         <v>334134</v>
       </c>
       <c r="O7" t="n">
-        <v>161853.45</v>
+        <v>163512.81</v>
       </c>
       <c r="P7" t="n">
         <v>370240.19</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>4200361.21</v>
+        <v>4207691.21</v>
       </c>
       <c r="P10" t="n">
         <v>7382808.04</v>
@@ -1792,10 +1792,10 @@
         <v>19028327.66</v>
       </c>
       <c r="S10" t="n">
-        <v>8788091.76</v>
+        <v>8790024.960000001</v>
       </c>
       <c r="T10" t="n">
-        <v>9703566.619999999</v>
+        <v>9705499.82</v>
       </c>
       <c r="U10" t="n">
         <v>11645519.62</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
         <v>768736.11</v>
       </c>
       <c r="S11" t="n">
-        <v>568286.11</v>
+        <v>486800</v>
       </c>
       <c r="T11" t="n">
         <v>650222.22</v>
@@ -1941,7 +1941,7 @@
         <v>568286.11</v>
       </c>
       <c r="V11" t="n">
-        <v>81936.11</v>
+        <v>163422.22</v>
       </c>
       <c r="W11" t="n">
         <v>569098</v>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1636725.56</v>
+        <v>1902011.17</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -6400,7 +6400,7 @@
         <v>131526</v>
       </c>
       <c r="O43" t="n">
-        <v>8172.88</v>
+        <v>8500.879999999999</v>
       </c>
       <c r="P43" t="n">
         <v>68092.11</v>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -7523,16 +7523,16 @@
         <v>7096288.58</v>
       </c>
       <c r="P51" t="n">
-        <v>4340670.78</v>
+        <v>4589956.52</v>
       </c>
       <c r="Q51" t="n">
         <v>278000</v>
       </c>
       <c r="R51" t="n">
-        <v>13632475.23</v>
+        <v>13881760.97</v>
       </c>
       <c r="S51" t="n">
-        <v>9291804.449999999</v>
+        <v>9042518.710000001</v>
       </c>
       <c r="T51" t="n">
         <v>11696727.44</v>
@@ -7541,7 +7541,7 @@
         <v>9291804.449999999</v>
       </c>
       <c r="V51" t="n">
-        <v>2404922.99</v>
+        <v>2654208.73</v>
       </c>
       <c r="W51" t="n">
         <v>9302683</v>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -14949,7 +14949,7 @@
         <v>268051</v>
       </c>
       <c r="R104" t="n">
-        <v>2190580.96</v>
+        <v>2198630.56</v>
       </c>
       <c r="S104" t="n">
         <v>2027342.68</v>
@@ -14958,7 +14958,7 @@
         <v>2027342.68</v>
       </c>
       <c r="U104" t="n">
-        <v>2182531.36</v>
+        <v>2190580.96</v>
       </c>
       <c r="V104" t="n">
         <v>0</v>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -20811,7 +20811,7 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>1296362.31</v>
+        <v>1297862.31</v>
       </c>
       <c r="M146" t="n">
         <v>0</v>
@@ -20820,7 +20820,7 @@
         <v>0</v>
       </c>
       <c r="O146" t="n">
-        <v>1265262.31</v>
+        <v>1273762.31</v>
       </c>
       <c r="P146" t="n">
         <v>15454293.91</v>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -21252,10 +21252,10 @@
         <v>107627.35</v>
       </c>
       <c r="S149" t="n">
-        <v>16605</v>
+        <v>18388</v>
       </c>
       <c r="T149" t="n">
-        <v>16605</v>
+        <v>18388</v>
       </c>
       <c r="U149" t="n">
         <v>107627.35</v>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -22232,10 +22232,10 @@
         <v>1038879.14</v>
       </c>
       <c r="S156" t="n">
-        <v>175845.16</v>
+        <v>176389.16</v>
       </c>
       <c r="T156" t="n">
-        <v>175845.16</v>
+        <v>176389.16</v>
       </c>
       <c r="U156" t="n">
         <v>359004.12</v>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -23900,7 +23900,7 @@
         <v>140000</v>
       </c>
       <c r="O168" t="n">
-        <v>0</v>
+        <v>138463.91</v>
       </c>
       <c r="P168" t="n">
         <v>0</v>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -25592,16 +25592,16 @@
         <v>267909.15</v>
       </c>
       <c r="S180" t="n">
-        <v>160506.12</v>
+        <v>161394.12</v>
       </c>
       <c r="T180" t="n">
-        <v>162300.12</v>
+        <v>164926.33</v>
       </c>
       <c r="U180" t="n">
         <v>221737.33</v>
       </c>
       <c r="V180" t="n">
-        <v>1794</v>
+        <v>3532.21</v>
       </c>
       <c r="W180" t="n">
         <v>252998</v>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -29491,7 +29491,7 @@
         </is>
       </c>
       <c r="L208" t="n">
-        <v>120276734.86</v>
+        <v>122248077.92</v>
       </c>
       <c r="M208" t="n">
         <v>0</v>
@@ -29500,7 +29500,7 @@
         <v>0</v>
       </c>
       <c r="O208" t="n">
-        <v>118161204.58</v>
+        <v>118180673.01</v>
       </c>
       <c r="P208" t="n">
         <v>49808521.04</v>
@@ -29512,10 +29512,10 @@
         <v>214390827.19</v>
       </c>
       <c r="S208" t="n">
-        <v>158557966.55</v>
+        <v>161627212.45</v>
       </c>
       <c r="T208" t="n">
-        <v>164225342.79</v>
+        <v>167294588.69</v>
       </c>
       <c r="U208" t="n">
         <v>164582306.15</v>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -29911,7 +29911,7 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>64701463.71</v>
+        <v>67129713.70999999</v>
       </c>
       <c r="M211" t="n">
         <v>0</v>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -30051,7 +30051,7 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>52542619.8</v>
+        <v>53802619.8</v>
       </c>
       <c r="M212" t="n">
         <v>0</v>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>18/08/2026 06:52:34</t>
+          <t>19/08/2026 06:48:48</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202608.xlsx
+++ b/base_despesas/2026/despesas_202608.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -1372,10 +1372,10 @@
         <v>1032083.64</v>
       </c>
       <c r="S7" t="n">
-        <v>308328.21</v>
+        <v>348078.21</v>
       </c>
       <c r="T7" t="n">
-        <v>413328.21</v>
+        <v>453078.21</v>
       </c>
       <c r="U7" t="n">
         <v>661843.45</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4602569.6</v>
+        <v>4802118.27</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3158787.61</v>
+        <v>3169590.08</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>9413730.609999999</v>
+        <v>9490082.289999999</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1902011.17</v>
+        <v>1906526.94</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -6400,7 +6400,7 @@
         <v>131526</v>
       </c>
       <c r="O43" t="n">
-        <v>8500.879999999999</v>
+        <v>8828.879999999999</v>
       </c>
       <c r="P43" t="n">
         <v>68092.11</v>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -6671,7 +6671,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2624273.45</v>
+        <v>2647227.22</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -11440,7 +11440,7 @@
         <v>80000</v>
       </c>
       <c r="O79" t="n">
-        <v>0</v>
+        <v>80000</v>
       </c>
       <c r="P79" t="n">
         <v>0</v>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -12697,7 +12697,7 @@
         <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>200000</v>
+        <v>499996</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -12724,7 +12724,7 @@
         <v>0</v>
       </c>
       <c r="W88" t="n">
-        <v>200000</v>
+        <v>499996</v>
       </c>
       <c r="X88" t="n">
         <v>0</v>
@@ -12736,7 +12736,7 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>200000</v>
+        <v>499996</v>
       </c>
       <c r="AB88" t="n">
         <v>5</v>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -14371,7 +14371,7 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>97826.36</v>
+        <v>113973.81</v>
       </c>
       <c r="M100" t="n">
         <v>0</v>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -18580,7 +18580,7 @@
         <v>280000</v>
       </c>
       <c r="O130" t="n">
-        <v>0</v>
+        <v>280000</v>
       </c>
       <c r="P130" t="n">
         <v>0</v>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -18720,7 +18720,7 @@
         <v>170000</v>
       </c>
       <c r="O131" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="P131" t="n">
         <v>0</v>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -19569,7 +19569,7 @@
         <v>0</v>
       </c>
       <c r="R137" t="n">
-        <v>7383237.78</v>
+        <v>9748668.68</v>
       </c>
       <c r="S137" t="n">
         <v>7383237.78</v>
@@ -19578,7 +19578,7 @@
         <v>7383237.78</v>
       </c>
       <c r="U137" t="n">
-        <v>7383237.78</v>
+        <v>9748668.68</v>
       </c>
       <c r="V137" t="n">
         <v>0</v>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -20951,7 +20951,7 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>1302862.31</v>
+        <v>1406637.56</v>
       </c>
       <c r="M147" t="n">
         <v>0</v>
@@ -20960,7 +20960,7 @@
         <v>0</v>
       </c>
       <c r="O147" t="n">
-        <v>1275262.31</v>
+        <v>1282362.31</v>
       </c>
       <c r="P147" t="n">
         <v>16179437.91</v>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -21231,7 +21231,7 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>39157.62</v>
+        <v>39514.57</v>
       </c>
       <c r="M149" t="n">
         <v>0</v>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -21651,7 +21651,7 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>202787.33</v>
+        <v>235377.76</v>
       </c>
       <c r="M152" t="n">
         <v>0</v>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -22640,7 +22640,7 @@
         <v>211572</v>
       </c>
       <c r="O159" t="n">
-        <v>1539184.16</v>
+        <v>1539344.16</v>
       </c>
       <c r="P159" t="n">
         <v>2681434.52</v>
@@ -22652,10 +22652,10 @@
         <v>6629661.87</v>
       </c>
       <c r="S159" t="n">
-        <v>2727398.96</v>
+        <v>2735398.96</v>
       </c>
       <c r="T159" t="n">
-        <v>2727718.96</v>
+        <v>2735718.96</v>
       </c>
       <c r="U159" t="n">
         <v>3948227.35</v>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -25869,16 +25869,16 @@
         <v>0</v>
       </c>
       <c r="R182" t="n">
-        <v>142934.93</v>
+        <v>144434.93</v>
       </c>
       <c r="S182" t="n">
-        <v>142934.93</v>
+        <v>144434.93</v>
       </c>
       <c r="T182" t="n">
-        <v>142934.93</v>
+        <v>144434.93</v>
       </c>
       <c r="U182" t="n">
-        <v>142934.93</v>
+        <v>144434.93</v>
       </c>
       <c r="V182" t="n">
         <v>0</v>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -27683,7 +27683,7 @@
         <v>255660.84</v>
       </c>
       <c r="P195" t="n">
-        <v>15229.89</v>
+        <v>1077378.91</v>
       </c>
       <c r="Q195" t="n">
         <v>5054381</v>
@@ -27698,7 +27698,7 @@
         <v>573554.02</v>
       </c>
       <c r="U195" t="n">
-        <v>5784251.52</v>
+        <v>4722102.5</v>
       </c>
       <c r="V195" t="n">
         <v>14256.24</v>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -28109,7 +28109,7 @@
         <v>39738</v>
       </c>
       <c r="R198" t="n">
-        <v>43800</v>
+        <v>44500</v>
       </c>
       <c r="S198" t="n">
         <v>31800</v>
@@ -28118,7 +28118,7 @@
         <v>32400</v>
       </c>
       <c r="U198" t="n">
-        <v>32400</v>
+        <v>33100</v>
       </c>
       <c r="V198" t="n">
         <v>600</v>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -28249,7 +28249,7 @@
         <v>0</v>
       </c>
       <c r="R199" t="n">
-        <v>52809.97</v>
+        <v>95090.62</v>
       </c>
       <c r="S199" t="n">
         <v>0</v>
@@ -28258,7 +28258,7 @@
         <v>0</v>
       </c>
       <c r="U199" t="n">
-        <v>33669</v>
+        <v>75949.64999999999</v>
       </c>
       <c r="V199" t="n">
         <v>0</v>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -28517,7 +28517,7 @@
         <v>0</v>
       </c>
       <c r="N201" t="n">
-        <v>0</v>
+        <v>170000</v>
       </c>
       <c r="O201" t="n">
         <v>0</v>
@@ -28544,7 +28544,7 @@
         <v>0</v>
       </c>
       <c r="W201" t="n">
-        <v>0</v>
+        <v>170000</v>
       </c>
       <c r="X201" t="n">
         <v>0</v>
@@ -28556,7 +28556,7 @@
         <v>0</v>
       </c>
       <c r="AA201" t="n">
-        <v>0</v>
+        <v>170000</v>
       </c>
       <c r="AB201" t="n">
         <v>5</v>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -29077,7 +29077,7 @@
         <v>0</v>
       </c>
       <c r="N205" t="n">
-        <v>5086650.13</v>
+        <v>5686650.13</v>
       </c>
       <c r="O205" t="n">
         <v>30296477.82</v>
@@ -29104,7 +29104,7 @@
         <v>0</v>
       </c>
       <c r="W205" t="n">
-        <v>45922205.13</v>
+        <v>46522205.13</v>
       </c>
       <c r="X205" t="n">
         <v>40835555</v>
@@ -29116,7 +29116,7 @@
         <v>0</v>
       </c>
       <c r="AA205" t="n">
-        <v>45922205.13</v>
+        <v>46522205.13</v>
       </c>
       <c r="AB205" t="n">
         <v>5</v>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -29244,7 +29244,7 @@
         <v>0</v>
       </c>
       <c r="W206" t="n">
-        <v>1200437</v>
+        <v>600437</v>
       </c>
       <c r="X206" t="n">
         <v>16896102</v>
@@ -29253,10 +29253,10 @@
         <v>16295665</v>
       </c>
       <c r="Z206" t="n">
-        <v>0</v>
+        <v>600000</v>
       </c>
       <c r="AA206" t="n">
-        <v>16896102</v>
+        <v>16296102</v>
       </c>
       <c r="AB206" t="n">
         <v>5</v>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -29640,7 +29640,7 @@
         <v>0</v>
       </c>
       <c r="O209" t="n">
-        <v>118286177.03</v>
+        <v>120257278.47</v>
       </c>
       <c r="P209" t="n">
         <v>49808521.04</v>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -30051,7 +30051,7 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>67129713.70999999</v>
+        <v>69557963.70999999</v>
       </c>
       <c r="M212" t="n">
         <v>0</v>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -30191,7 +30191,7 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>53892619.8</v>
+        <v>53966773.95</v>
       </c>
       <c r="M213" t="n">
         <v>0</v>
@@ -30200,7 +30200,7 @@
         <v>0</v>
       </c>
       <c r="O213" t="n">
-        <v>47621025.9</v>
+        <v>48611025.9</v>
       </c>
       <c r="P213" t="n">
         <v>50438263.91</v>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>
@@ -31180,7 +31180,7 @@
         <v>0</v>
       </c>
       <c r="O220" t="n">
-        <v>34814362.52</v>
+        <v>34876296.58</v>
       </c>
       <c r="P220" t="n">
         <v>6388346.56</v>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>20/08/2026 06:55:21</t>
+          <t>21/08/2026 06:53:45</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202608.xlsx
+++ b/base_despesas/2026/despesas_202608.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4802118.27</v>
+        <v>4808067.53</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1780,16 +1780,16 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>4376097.02</v>
+        <v>4386053.26</v>
       </c>
       <c r="P10" t="n">
-        <v>7443256.67</v>
+        <v>7482256.67</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>19076871.32</v>
+        <v>19106233.85</v>
       </c>
       <c r="S10" t="n">
         <v>9158598.369999999</v>
@@ -1798,7 +1798,7 @@
         <v>10086227.23</v>
       </c>
       <c r="U10" t="n">
-        <v>11633614.65</v>
+        <v>11623977.18</v>
       </c>
       <c r="V10" t="n">
         <v>927628.86</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3169590.08</v>
+        <v>3509598.53</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -4869,16 +4869,16 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>23401872.01</v>
+        <v>23433205.31</v>
       </c>
       <c r="S32" t="n">
-        <v>17034593.44</v>
+        <v>17042066.08</v>
       </c>
       <c r="T32" t="n">
-        <v>20548620.15</v>
+        <v>20556092.79</v>
       </c>
       <c r="U32" t="n">
-        <v>17754824.84</v>
+        <v>17786158.14</v>
       </c>
       <c r="V32" t="n">
         <v>3514026.71</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -5140,7 +5140,7 @@
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>68417.64999999999</v>
+        <v>82538.81</v>
       </c>
       <c r="P34" t="n">
         <v>0</v>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -5420,7 +5420,7 @@
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>1636725.56</v>
+        <v>1906526.94</v>
       </c>
       <c r="P36" t="n">
         <v>2931914.44</v>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>10313.28</v>
+        <v>10641.28</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -6671,7 +6671,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2647227.22</v>
+        <v>2647296.32</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -6811,7 +6811,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>138905.68</v>
+        <v>146026.49</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>22580.62</v>
+        <v>23342.56</v>
       </c>
       <c r="M54" t="n">
         <v>0</v>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -8500,7 +8500,7 @@
         <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>6600922.5</v>
+        <v>8643538.5</v>
       </c>
       <c r="P58" t="n">
         <v>7316405.83</v>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -11729,7 +11729,7 @@
         <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>250000</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -11738,7 +11738,7 @@
         <v>0</v>
       </c>
       <c r="U81" t="n">
-        <v>0</v>
+        <v>250000</v>
       </c>
       <c r="V81" t="n">
         <v>0</v>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -14371,7 +14371,7 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>113973.81</v>
+        <v>114042.91</v>
       </c>
       <c r="M100" t="n">
         <v>0</v>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -16060,7 +16060,7 @@
         <v>90000</v>
       </c>
       <c r="O112" t="n">
-        <v>0</v>
+        <v>90000</v>
       </c>
       <c r="P112" t="n">
         <v>0</v>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -19560,7 +19560,7 @@
         <v>0</v>
       </c>
       <c r="O137" t="n">
-        <v>6282898.35</v>
+        <v>7195593.68</v>
       </c>
       <c r="P137" t="n">
         <v>0</v>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -20960,7 +20960,7 @@
         <v>0</v>
       </c>
       <c r="O147" t="n">
-        <v>1282362.31</v>
+        <v>1288862.31</v>
       </c>
       <c r="P147" t="n">
         <v>16179437.91</v>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -21651,7 +21651,7 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>235377.76</v>
+        <v>236546.44</v>
       </c>
       <c r="M152" t="n">
         <v>0</v>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -22351,7 +22351,7 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>74047.78999999999</v>
+        <v>74375.78999999999</v>
       </c>
       <c r="M157" t="n">
         <v>0</v>
@@ -22360,7 +22360,7 @@
         <v>259262</v>
       </c>
       <c r="O157" t="n">
-        <v>46435.29</v>
+        <v>46763.29</v>
       </c>
       <c r="P157" t="n">
         <v>679875.02</v>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -22631,7 +22631,7 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>1556687.74</v>
+        <v>1577353.12</v>
       </c>
       <c r="M159" t="n">
         <v>0</v>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -24189,7 +24189,7 @@
         <v>0</v>
       </c>
       <c r="R170" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="S170" t="n">
         <v>0</v>
@@ -24198,7 +24198,7 @@
         <v>0</v>
       </c>
       <c r="U170" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="V170" t="n">
         <v>0</v>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -26131,7 +26131,7 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>1520667.89</v>
+        <v>1520782.37</v>
       </c>
       <c r="M184" t="n">
         <v>0</v>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -27671,7 +27671,7 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>255840.54</v>
+        <v>273660.67</v>
       </c>
       <c r="M195" t="n">
         <v>0</v>
@@ -27683,25 +27683,25 @@
         <v>255660.84</v>
       </c>
       <c r="P195" t="n">
-        <v>1077378.91</v>
+        <v>2957320.94</v>
       </c>
       <c r="Q195" t="n">
         <v>5054381</v>
       </c>
       <c r="R195" t="n">
-        <v>5799481.41</v>
+        <v>7679423.44</v>
       </c>
       <c r="S195" t="n">
-        <v>559297.78</v>
+        <v>2439551.17</v>
       </c>
       <c r="T195" t="n">
-        <v>573554.02</v>
+        <v>2453838.77</v>
       </c>
       <c r="U195" t="n">
         <v>4722102.5</v>
       </c>
       <c r="V195" t="n">
-        <v>14256.24</v>
+        <v>14287.6</v>
       </c>
       <c r="W195" t="n">
         <v>5866355</v>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -29089,7 +29089,7 @@
         <v>0</v>
       </c>
       <c r="R205" t="n">
-        <v>45922205.13</v>
+        <v>46522205.13</v>
       </c>
       <c r="S205" t="n">
         <v>45922205.12</v>
@@ -29098,7 +29098,7 @@
         <v>45922205.12</v>
       </c>
       <c r="U205" t="n">
-        <v>45922205.13</v>
+        <v>46522205.13</v>
       </c>
       <c r="V205" t="n">
         <v>0</v>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -29631,7 +29631,7 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>122248077.92</v>
+        <v>126289723.58</v>
       </c>
       <c r="M209" t="n">
         <v>0</v>
@@ -29640,7 +29640,7 @@
         <v>0</v>
       </c>
       <c r="O209" t="n">
-        <v>120257278.47</v>
+        <v>120276734.86</v>
       </c>
       <c r="P209" t="n">
         <v>49808521.04</v>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -30191,7 +30191,7 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>53966773.95</v>
+        <v>54471982.83</v>
       </c>
       <c r="M213" t="n">
         <v>0</v>
@@ -30200,7 +30200,7 @@
         <v>0</v>
       </c>
       <c r="O213" t="n">
-        <v>48611025.9</v>
+        <v>52388025.9</v>
       </c>
       <c r="P213" t="n">
         <v>50438263.91</v>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>21/08/2026 06:53:45</t>
+          <t>22/08/2026 06:47:23</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202608.xlsx
+++ b/base_despesas/2026/despesas_202608.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>22/08/2026 06:47:23</t>
+          <t>23/08/2026 06:41:10</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202608.xlsx
+++ b/base_despesas/2026/despesas_202608.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>23/08/2026 06:41:10</t>
+          <t>24/08/2026 10:11:58</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202608.xlsx
+++ b/base_despesas/2026/despesas_202608.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -1223,13 +1223,13 @@
         <v>77609.89</v>
       </c>
       <c r="P6" t="n">
-        <v>23626.09</v>
+        <v>24053.29</v>
       </c>
       <c r="Q6" t="n">
         <v>46024</v>
       </c>
       <c r="R6" t="n">
-        <v>101235.98</v>
+        <v>102731.18</v>
       </c>
       <c r="S6" t="n">
         <v>77609.89</v>
@@ -1238,7 +1238,7 @@
         <v>94035.98</v>
       </c>
       <c r="U6" t="n">
-        <v>77609.89</v>
+        <v>78677.89</v>
       </c>
       <c r="V6" t="n">
         <v>16426.09</v>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -1363,13 +1363,13 @@
         <v>163512.81</v>
       </c>
       <c r="P7" t="n">
-        <v>370240.19</v>
+        <v>377087.59</v>
       </c>
       <c r="Q7" t="n">
         <v>63262</v>
       </c>
       <c r="R7" t="n">
-        <v>1032083.64</v>
+        <v>1038931.04</v>
       </c>
       <c r="S7" t="n">
         <v>348078.21</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>295928.97</v>
       </c>
       <c r="O10" t="n">
         <v>4386053.26</v>
@@ -1789,7 +1789,7 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>19106233.85</v>
+        <v>19421689.71</v>
       </c>
       <c r="S10" t="n">
         <v>9158598.369999999</v>
@@ -1798,13 +1798,13 @@
         <v>10086227.23</v>
       </c>
       <c r="U10" t="n">
-        <v>11623977.18</v>
+        <v>11939433.04</v>
       </c>
       <c r="V10" t="n">
         <v>927628.86</v>
       </c>
       <c r="W10" t="n">
-        <v>11656658.15</v>
+        <v>11952587.12</v>
       </c>
       <c r="X10" t="n">
         <v>15575058</v>
@@ -1816,7 +1816,7 @@
         <v>791391.85</v>
       </c>
       <c r="AA10" t="n">
-        <v>14783666.15</v>
+        <v>15079595.12</v>
       </c>
       <c r="AB10" t="n">
         <v>5</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -4577,19 +4577,19 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>261000</v>
       </c>
       <c r="O30" t="n">
         <v>1142642.78</v>
       </c>
       <c r="P30" t="n">
-        <v>641271.01</v>
+        <v>652630.21</v>
       </c>
       <c r="Q30" t="n">
         <v>9180</v>
       </c>
       <c r="R30" t="n">
-        <v>2482383.88</v>
+        <v>2566214.6</v>
       </c>
       <c r="S30" t="n">
         <v>1718528.16</v>
@@ -4598,13 +4598,13 @@
         <v>1875118.94</v>
       </c>
       <c r="U30" t="n">
-        <v>1841112.87</v>
+        <v>1913584.39</v>
       </c>
       <c r="V30" t="n">
         <v>156590.78</v>
       </c>
       <c r="W30" t="n">
-        <v>1841736</v>
+        <v>2102736</v>
       </c>
       <c r="X30" t="n">
         <v>1841736</v>
@@ -4616,7 +4616,7 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1841736</v>
+        <v>2102736</v>
       </c>
       <c r="AB30" t="n">
         <v>5</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -4872,10 +4872,10 @@
         <v>23433205.31</v>
       </c>
       <c r="S32" t="n">
-        <v>17042066.08</v>
+        <v>17057786.73</v>
       </c>
       <c r="T32" t="n">
-        <v>20556092.79</v>
+        <v>20571813.44</v>
       </c>
       <c r="U32" t="n">
         <v>17786158.14</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -6409,7 +6409,7 @@
         <v>22671</v>
       </c>
       <c r="R43" t="n">
-        <v>260197.34</v>
+        <v>263322.54</v>
       </c>
       <c r="S43" t="n">
         <v>51657</v>
@@ -6418,7 +6418,7 @@
         <v>55593</v>
       </c>
       <c r="U43" t="n">
-        <v>192105.23</v>
+        <v>195230.43</v>
       </c>
       <c r="V43" t="n">
         <v>3936</v>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -7511,7 +7511,7 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>7096288.58</v>
+        <v>7363410.03</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -14404,7 +14404,7 @@
         <v>1350</v>
       </c>
       <c r="W100" t="n">
-        <v>505872.78</v>
+        <v>355872.78</v>
       </c>
       <c r="X100" t="n">
         <v>1314953</v>
@@ -14413,10 +14413,10 @@
         <v>719080.22</v>
       </c>
       <c r="Z100" t="n">
-        <v>90000</v>
+        <v>240000</v>
       </c>
       <c r="AA100" t="n">
-        <v>1224953</v>
+        <v>1074953</v>
       </c>
       <c r="AB100" t="n">
         <v>5</v>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -16349,7 +16349,7 @@
         <v>0</v>
       </c>
       <c r="R114" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -16358,7 +16358,7 @@
         <v>0</v>
       </c>
       <c r="U114" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="V114" t="n">
         <v>0</v>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -22369,7 +22369,7 @@
         <v>8077</v>
       </c>
       <c r="R157" t="n">
-        <v>1038879.14</v>
+        <v>1049519.14</v>
       </c>
       <c r="S157" t="n">
         <v>176389.16</v>
@@ -22378,7 +22378,7 @@
         <v>176389.16</v>
       </c>
       <c r="U157" t="n">
-        <v>359004.12</v>
+        <v>369644.12</v>
       </c>
       <c r="V157" t="n">
         <v>0</v>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -24612,10 +24612,10 @@
         <v>578000</v>
       </c>
       <c r="S173" t="n">
-        <v>200000</v>
+        <v>350000</v>
       </c>
       <c r="T173" t="n">
-        <v>200000</v>
+        <v>350000</v>
       </c>
       <c r="U173" t="n">
         <v>578000</v>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -26149,7 +26149,7 @@
         <v>0</v>
       </c>
       <c r="R184" t="n">
-        <v>5517841.82</v>
+        <v>5560336.16</v>
       </c>
       <c r="S184" t="n">
         <v>2403429.22</v>
@@ -26158,13 +26158,13 @@
         <v>2507776.98</v>
       </c>
       <c r="U184" t="n">
-        <v>3285255.11</v>
+        <v>3327749.45</v>
       </c>
       <c r="V184" t="n">
         <v>104347.76</v>
       </c>
       <c r="W184" t="n">
-        <v>3735019</v>
+        <v>3328090.03</v>
       </c>
       <c r="X184" t="n">
         <v>4806049</v>
@@ -26173,10 +26173,10 @@
         <v>65487</v>
       </c>
       <c r="Z184" t="n">
-        <v>1005543</v>
+        <v>1412471.97</v>
       </c>
       <c r="AA184" t="n">
-        <v>3800506</v>
+        <v>3393577.03</v>
       </c>
       <c r="AB184" t="n">
         <v>5</v>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -28112,10 +28112,10 @@
         <v>44500</v>
       </c>
       <c r="S198" t="n">
-        <v>31800</v>
+        <v>32500</v>
       </c>
       <c r="T198" t="n">
-        <v>32400</v>
+        <v>33100</v>
       </c>
       <c r="U198" t="n">
         <v>33100</v>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -29649,16 +29649,16 @@
         <v>5086650.13</v>
       </c>
       <c r="R209" t="n">
-        <v>214390827.19</v>
+        <v>214390827.25</v>
       </c>
       <c r="S209" t="n">
-        <v>162723371.7</v>
+        <v>162723371.76</v>
       </c>
       <c r="T209" t="n">
-        <v>168390747.94</v>
+        <v>168390748</v>
       </c>
       <c r="U209" t="n">
-        <v>164582306.15</v>
+        <v>164582306.21</v>
       </c>
       <c r="V209" t="n">
         <v>5667376.24</v>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>
@@ -31171,7 +31171,7 @@
         </is>
       </c>
       <c r="L220" t="n">
-        <v>35122742.46</v>
+        <v>35362303.78</v>
       </c>
       <c r="M220" t="n">
         <v>0</v>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>24/08/2026 10:11:58</t>
+          <t>25/08/2026 06:51:23</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202608.xlsx
+++ b/base_despesas/2026/despesas_202608.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4561253.34</v>
+        <v>5068732.62</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>77609.89</v>
+        <v>78677.89</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1229,16 +1229,16 @@
         <v>46024</v>
       </c>
       <c r="R6" t="n">
-        <v>102731.18</v>
+        <v>103799.18</v>
       </c>
       <c r="S6" t="n">
-        <v>77609.89</v>
+        <v>78677.89</v>
       </c>
       <c r="T6" t="n">
-        <v>94035.98</v>
+        <v>95103.98</v>
       </c>
       <c r="U6" t="n">
-        <v>78677.89</v>
+        <v>79745.89</v>
       </c>
       <c r="V6" t="n">
         <v>16426.09</v>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4813203.83</v>
+        <v>4816262.43</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1780,16 +1780,16 @@
         <v>295928.97</v>
       </c>
       <c r="O10" t="n">
-        <v>4390048.26</v>
+        <v>4390075.61</v>
       </c>
       <c r="P10" t="n">
-        <v>7482256.67</v>
+        <v>7797712.53</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3096601.89</v>
       </c>
       <c r="R10" t="n">
-        <v>19421689.71</v>
+        <v>19737145.57</v>
       </c>
       <c r="S10" t="n">
         <v>9158598.369999999</v>
@@ -1804,7 +1804,7 @@
         <v>927628.86</v>
       </c>
       <c r="W10" t="n">
-        <v>11952587.12</v>
+        <v>15049189.01</v>
       </c>
       <c r="X10" t="n">
         <v>15575058</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>181130.98</v>
+        <v>181205.98</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1920,7 +1920,7 @@
         <v>197487</v>
       </c>
       <c r="O11" t="n">
-        <v>126906.71</v>
+        <v>162601.92</v>
       </c>
       <c r="P11" t="n">
         <v>200450</v>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>182059.94</v>
+        <v>182179.94</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -4011,7 +4011,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>9307870.02</v>
+        <v>10570590.51</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -4029,16 +4029,16 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>9309375.279999999</v>
+        <v>10572095.77</v>
       </c>
       <c r="S26" t="n">
-        <v>9309375.279999999</v>
+        <v>10572095.77</v>
       </c>
       <c r="T26" t="n">
-        <v>9309375.279999999</v>
+        <v>10572095.77</v>
       </c>
       <c r="U26" t="n">
-        <v>9309375.279999999</v>
+        <v>10572095.77</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -4571,7 +4571,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1142642.78</v>
+        <v>1145867.82</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -4583,22 +4583,22 @@
         <v>1142642.78</v>
       </c>
       <c r="P30" t="n">
-        <v>652630.21</v>
+        <v>652919.54</v>
       </c>
       <c r="Q30" t="n">
         <v>9180</v>
       </c>
       <c r="R30" t="n">
-        <v>2566214.6</v>
+        <v>2600214.6</v>
       </c>
       <c r="S30" t="n">
-        <v>1718528.16</v>
+        <v>1778615.7</v>
       </c>
       <c r="T30" t="n">
-        <v>1875118.94</v>
+        <v>1935206.48</v>
       </c>
       <c r="U30" t="n">
-        <v>1913584.39</v>
+        <v>1947295.06</v>
       </c>
       <c r="V30" t="n">
         <v>156590.78</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>9490082.289999999</v>
+        <v>9491055.880000001</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -4863,13 +4863,13 @@
         <v>8574427.300000001</v>
       </c>
       <c r="P32" t="n">
-        <v>5647047.17</v>
+        <v>5847047.17</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>23433205.31</v>
+        <v>24425135.57</v>
       </c>
       <c r="S32" t="n">
         <v>17057786.73</v>
@@ -4878,7 +4878,7 @@
         <v>20571813.44</v>
       </c>
       <c r="U32" t="n">
-        <v>17786158.14</v>
+        <v>18578088.4</v>
       </c>
       <c r="V32" t="n">
         <v>3514026.71</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -4991,7 +4991,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>433920.41</v>
+        <v>438489.3</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -5000,7 +5000,7 @@
         <v>110000</v>
       </c>
       <c r="O33" t="n">
-        <v>383342.27</v>
+        <v>411227.58</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -5271,7 +5271,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2611298.09</v>
+        <v>2986467.8</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -5289,16 +5289,16 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>2611298.09</v>
+        <v>2986467.8</v>
       </c>
       <c r="S35" t="n">
-        <v>2611298.09</v>
+        <v>2986467.8</v>
       </c>
       <c r="T35" t="n">
-        <v>2611298.09</v>
+        <v>2986467.8</v>
       </c>
       <c r="U35" t="n">
-        <v>2611298.09</v>
+        <v>2986467.8</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -6403,13 +6403,13 @@
         <v>8828.879999999999</v>
       </c>
       <c r="P43" t="n">
-        <v>68092.11</v>
+        <v>98795.48</v>
       </c>
       <c r="Q43" t="n">
         <v>22671</v>
       </c>
       <c r="R43" t="n">
-        <v>263322.54</v>
+        <v>327572.54</v>
       </c>
       <c r="S43" t="n">
         <v>51657</v>
@@ -6418,7 +6418,7 @@
         <v>55593</v>
       </c>
       <c r="U43" t="n">
-        <v>195230.43</v>
+        <v>228777.06</v>
       </c>
       <c r="V43" t="n">
         <v>3936</v>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
         <v>16620780.47</v>
       </c>
       <c r="Q45" t="n">
-        <v>1186346</v>
+        <v>5379029</v>
       </c>
       <c r="R45" t="n">
         <v>31080819.1</v>
@@ -6704,7 +6704,7 @@
         <v>433277.15</v>
       </c>
       <c r="W45" t="n">
-        <v>14470561.05</v>
+        <v>18663244.05</v>
       </c>
       <c r="X45" t="n">
         <v>21072104</v>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -6820,7 +6820,7 @@
         <v>219000</v>
       </c>
       <c r="O46" t="n">
-        <v>129469.64</v>
+        <v>144399.42</v>
       </c>
       <c r="P46" t="n">
         <v>0</v>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -7940,7 +7940,7 @@
         <v>50000</v>
       </c>
       <c r="O54" t="n">
-        <v>20732.28</v>
+        <v>22387.93</v>
       </c>
       <c r="P54" t="n">
         <v>0</v>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -8229,7 +8229,7 @@
         <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>330000</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -8238,7 +8238,7 @@
         <v>0</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>330000</v>
       </c>
       <c r="V56" t="n">
         <v>0</v>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -12572,10 +12572,10 @@
         <v>2884872.14</v>
       </c>
       <c r="S87" t="n">
-        <v>5577</v>
+        <v>1885519.03</v>
       </c>
       <c r="T87" t="n">
-        <v>5577</v>
+        <v>1885519.03</v>
       </c>
       <c r="U87" t="n">
         <v>1931484.4</v>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -12837,7 +12837,7 @@
         <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>190000</v>
+        <v>260000</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -12864,7 +12864,7 @@
         <v>0</v>
       </c>
       <c r="W89" t="n">
-        <v>190000</v>
+        <v>260000</v>
       </c>
       <c r="X89" t="n">
         <v>0</v>
@@ -12876,7 +12876,7 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>190000</v>
+        <v>260000</v>
       </c>
       <c r="AB89" t="n">
         <v>5</v>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -14940,7 +14940,7 @@
         <v>40000</v>
       </c>
       <c r="O104" t="n">
-        <v>5467.34</v>
+        <v>6447.95</v>
       </c>
       <c r="P104" t="n">
         <v>450</v>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -18020,7 +18020,7 @@
         <v>360000</v>
       </c>
       <c r="O126" t="n">
-        <v>0</v>
+        <v>360000</v>
       </c>
       <c r="P126" t="n">
         <v>0</v>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -19703,13 +19703,13 @@
         <v>0</v>
       </c>
       <c r="P138" t="n">
-        <v>40903.05</v>
+        <v>294610.65</v>
       </c>
       <c r="Q138" t="n">
         <v>0</v>
       </c>
       <c r="R138" t="n">
-        <v>419535.05</v>
+        <v>673242.65</v>
       </c>
       <c r="S138" t="n">
         <v>3852</v>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -21511,7 +21511,7 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>1406637.56</v>
+        <v>1411637.56</v>
       </c>
       <c r="M151" t="n">
         <v>0</v>
@@ -21520,7 +21520,7 @@
         <v>0</v>
       </c>
       <c r="O151" t="n">
-        <v>1294862.31</v>
+        <v>1301362.31</v>
       </c>
       <c r="P151" t="n">
         <v>16179437.91</v>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -22360,7 +22360,7 @@
         <v>50000</v>
       </c>
       <c r="O157" t="n">
-        <v>24857.24</v>
+        <v>27215.98</v>
       </c>
       <c r="P157" t="n">
         <v>2250</v>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -22911,7 +22911,7 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>74375.78999999999</v>
+        <v>133731.79</v>
       </c>
       <c r="M161" t="n">
         <v>0</v>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -23191,7 +23191,7 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>1657091.44</v>
+        <v>1772047.84</v>
       </c>
       <c r="M163" t="n">
         <v>0</v>
@@ -23200,7 +23200,7 @@
         <v>211572</v>
       </c>
       <c r="O163" t="n">
-        <v>1539344.16</v>
+        <v>1554642.66</v>
       </c>
       <c r="P163" t="n">
         <v>2681434.52</v>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -25860,7 +25860,7 @@
         <v>712872.0600000001</v>
       </c>
       <c r="O182" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="P182" t="n">
         <v>0</v>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -26000,7 +26000,7 @@
         <v>318150</v>
       </c>
       <c r="O183" t="n">
-        <v>0</v>
+        <v>318150</v>
       </c>
       <c r="P183" t="n">
         <v>0</v>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -26271,7 +26271,7 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>24306394.23</v>
+        <v>24545612.47</v>
       </c>
       <c r="M185" t="n">
         <v>0</v>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -26831,7 +26831,7 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>1520782.37</v>
+        <v>1540908.15</v>
       </c>
       <c r="M189" t="n">
         <v>0</v>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -28100,7 +28100,7 @@
         <v>0</v>
       </c>
       <c r="O198" t="n">
-        <v>0</v>
+        <v>9864</v>
       </c>
       <c r="P198" t="n">
         <v>0</v>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -28392,7 +28392,7 @@
         <v>7689959.02</v>
       </c>
       <c r="S200" t="n">
-        <v>2439551.17</v>
+        <v>559609.14</v>
       </c>
       <c r="T200" t="n">
         <v>2453838.77</v>
@@ -28401,7 +28401,7 @@
         <v>4732638.08</v>
       </c>
       <c r="V200" t="n">
-        <v>14287.6</v>
+        <v>1894229.63</v>
       </c>
       <c r="W200" t="n">
         <v>4801538</v>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -29926,7 +29926,7 @@
         <v>0</v>
       </c>
       <c r="Q211" t="n">
-        <v>600000</v>
+        <v>16295665</v>
       </c>
       <c r="R211" t="n">
         <v>0</v>
@@ -29944,7 +29944,7 @@
         <v>0</v>
       </c>
       <c r="W211" t="n">
-        <v>600437</v>
+        <v>16296102</v>
       </c>
       <c r="X211" t="n">
         <v>16896102</v>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -30331,7 +30331,7 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>126289723.58</v>
+        <v>135644990.41</v>
       </c>
       <c r="M214" t="n">
         <v>0</v>
@@ -30340,7 +30340,7 @@
         <v>0</v>
       </c>
       <c r="O214" t="n">
-        <v>120276734.86</v>
+        <v>122365035.28</v>
       </c>
       <c r="P214" t="n">
         <v>49808521.04</v>
@@ -30352,10 +30352,10 @@
         <v>214390827.25</v>
       </c>
       <c r="S214" t="n">
-        <v>162723371.76</v>
+        <v>163819531.01</v>
       </c>
       <c r="T214" t="n">
-        <v>168390748</v>
+        <v>169486907.25</v>
       </c>
       <c r="U214" t="n">
         <v>164582306.21</v>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -30751,7 +30751,7 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>69557963.70999999</v>
+        <v>71986213.70999999</v>
       </c>
       <c r="M217" t="n">
         <v>0</v>
@@ -30760,13 +30760,13 @@
         <v>0</v>
       </c>
       <c r="O217" t="n">
-        <v>62273213.71</v>
+        <v>67129713.70999999</v>
       </c>
       <c r="P217" t="n">
         <v>62818272</v>
       </c>
       <c r="Q217" t="n">
-        <v>0</v>
+        <v>4727853</v>
       </c>
       <c r="R217" t="n">
         <v>199707294</v>
@@ -30784,7 +30784,7 @@
         <v>0</v>
       </c>
       <c r="W217" t="n">
-        <v>136889022</v>
+        <v>141616875</v>
       </c>
       <c r="X217" t="n">
         <v>141616875</v>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -30891,7 +30891,7 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>54471982.83</v>
+        <v>54651982.83</v>
       </c>
       <c r="M218" t="n">
         <v>0</v>
@@ -30900,7 +30900,7 @@
         <v>0</v>
       </c>
       <c r="O218" t="n">
-        <v>52388025.9</v>
+        <v>53892619.8</v>
       </c>
       <c r="P218" t="n">
         <v>50438263.91</v>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -31394,7 +31394,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -31534,7 +31534,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -31674,7 +31674,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>
@@ -31889,7 +31889,7 @@
         <v>0</v>
       </c>
       <c r="R225" t="n">
-        <v>47237841.52</v>
+        <v>48542457.07</v>
       </c>
       <c r="S225" t="n">
         <v>38990514.67</v>
@@ -31898,7 +31898,7 @@
         <v>40603278.83</v>
       </c>
       <c r="U225" t="n">
-        <v>40849494.96</v>
+        <v>42154110.51</v>
       </c>
       <c r="V225" t="n">
         <v>1612764.16</v>
@@ -31954,7 +31954,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>26/08/2026 07:05:51</t>
+          <t>28/08/2026 18:00:38</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202608.xlsx
+++ b/base_despesas/2026/despesas_202608.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>78677.89</v>
+        <v>79745.89</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1232,10 +1232,10 @@
         <v>103799.18</v>
       </c>
       <c r="S6" t="n">
-        <v>78677.89</v>
+        <v>79745.89</v>
       </c>
       <c r="T6" t="n">
-        <v>95103.98</v>
+        <v>96171.98</v>
       </c>
       <c r="U6" t="n">
         <v>79745.89</v>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>163512.81</v>
+        <v>164072.81</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
         <v>295928.97</v>
       </c>
       <c r="O10" t="n">
-        <v>4390075.61</v>
+        <v>4422561.28</v>
       </c>
       <c r="P10" t="n">
         <v>7797712.53</v>
@@ -1792,10 +1792,10 @@
         <v>19737145.57</v>
       </c>
       <c r="S10" t="n">
-        <v>9158598.369999999</v>
+        <v>9608225.01</v>
       </c>
       <c r="T10" t="n">
-        <v>10086227.23</v>
+        <v>10535853.87</v>
       </c>
       <c r="U10" t="n">
         <v>11939433.04</v>
@@ -1804,7 +1804,7 @@
         <v>927628.86</v>
       </c>
       <c r="W10" t="n">
-        <v>15049189.01</v>
+        <v>11952587.12</v>
       </c>
       <c r="X10" t="n">
         <v>15575058</v>
@@ -1813,10 +1813,10 @@
         <v>3127008</v>
       </c>
       <c r="Z10" t="n">
-        <v>791391.85</v>
+        <v>3887993.74</v>
       </c>
       <c r="AA10" t="n">
-        <v>15079595.12</v>
+        <v>11982993.23</v>
       </c>
       <c r="AB10" t="n">
         <v>5</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>181205.98</v>
+        <v>182618.64</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
         <v>725144</v>
       </c>
       <c r="O32" t="n">
-        <v>8574427.300000001</v>
+        <v>8651702.98</v>
       </c>
       <c r="P32" t="n">
         <v>5847047.17</v>
@@ -4872,10 +4872,10 @@
         <v>24425135.57</v>
       </c>
       <c r="S32" t="n">
-        <v>17057786.73</v>
+        <v>17196108.7</v>
       </c>
       <c r="T32" t="n">
-        <v>20571813.44</v>
+        <v>20710135.41</v>
       </c>
       <c r="U32" t="n">
         <v>18578088.4</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -6671,7 +6671,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2710980.12</v>
+        <v>2730193.85</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -6683,7 +6683,7 @@
         <v>2499309.9</v>
       </c>
       <c r="P45" t="n">
-        <v>16620780.47</v>
+        <v>16770780.47</v>
       </c>
       <c r="Q45" t="n">
         <v>5379029</v>
@@ -6692,19 +6692,19 @@
         <v>31080819.1</v>
       </c>
       <c r="S45" t="n">
-        <v>5343661.24</v>
+        <v>5410326.73</v>
       </c>
       <c r="T45" t="n">
-        <v>5776938.39</v>
+        <v>5843603.88</v>
       </c>
       <c r="U45" t="n">
-        <v>14460038.63</v>
+        <v>14310038.63</v>
       </c>
       <c r="V45" t="n">
         <v>433277.15</v>
       </c>
       <c r="W45" t="n">
-        <v>18663244.05</v>
+        <v>14470561.05</v>
       </c>
       <c r="X45" t="n">
         <v>21072104</v>
@@ -6713,10 +6713,10 @@
         <v>5379029</v>
       </c>
       <c r="Z45" t="n">
-        <v>2502745.95</v>
+        <v>6695428.95</v>
       </c>
       <c r="AA45" t="n">
-        <v>18663244.05</v>
+        <v>14470561.05</v>
       </c>
       <c r="AB45" t="n">
         <v>5</v>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -13972,10 +13972,10 @@
         <v>22092.87</v>
       </c>
       <c r="S97" t="n">
-        <v>0</v>
+        <v>22092.87</v>
       </c>
       <c r="T97" t="n">
-        <v>0</v>
+        <v>22092.87</v>
       </c>
       <c r="U97" t="n">
         <v>22092.87</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -19149,7 +19149,7 @@
         <v>0</v>
       </c>
       <c r="R134" t="n">
-        <v>100000</v>
+        <v>170000</v>
       </c>
       <c r="S134" t="n">
         <v>100000</v>
@@ -19158,7 +19158,7 @@
         <v>100000</v>
       </c>
       <c r="U134" t="n">
-        <v>100000</v>
+        <v>170000</v>
       </c>
       <c r="V134" t="n">
         <v>0</v>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -21520,7 +21520,7 @@
         <v>0</v>
       </c>
       <c r="O151" t="n">
-        <v>1301362.31</v>
+        <v>1405137.56</v>
       </c>
       <c r="P151" t="n">
         <v>16179437.91</v>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -22360,7 +22360,7 @@
         <v>50000</v>
       </c>
       <c r="O157" t="n">
-        <v>27215.98</v>
+        <v>27370.11</v>
       </c>
       <c r="P157" t="n">
         <v>2250</v>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -23212,10 +23212,10 @@
         <v>6629661.87</v>
       </c>
       <c r="S163" t="n">
-        <v>2735398.96</v>
+        <v>2878721.84</v>
       </c>
       <c r="T163" t="n">
-        <v>2735718.96</v>
+        <v>2879041.84</v>
       </c>
       <c r="U163" t="n">
         <v>3948227.35</v>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="R180" t="n">
-        <v>150000</v>
+        <v>261000</v>
       </c>
       <c r="S180" t="n">
         <v>0</v>
@@ -25598,7 +25598,7 @@
         <v>0</v>
       </c>
       <c r="U180" t="n">
-        <v>150000</v>
+        <v>261000</v>
       </c>
       <c r="V180" t="n">
         <v>0</v>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -26831,7 +26831,7 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>1540908.15</v>
+        <v>1573472.63</v>
       </c>
       <c r="M189" t="n">
         <v>0</v>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -28371,7 +28371,7 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>273660.67</v>
+        <v>318270.87</v>
       </c>
       <c r="M200" t="n">
         <v>0</v>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -29944,7 +29944,7 @@
         <v>0</v>
       </c>
       <c r="W211" t="n">
-        <v>16296102</v>
+        <v>600437</v>
       </c>
       <c r="X211" t="n">
         <v>16896102</v>
@@ -29953,10 +29953,10 @@
         <v>16295665</v>
       </c>
       <c r="Z211" t="n">
-        <v>600000</v>
+        <v>16295665</v>
       </c>
       <c r="AA211" t="n">
-        <v>16296102</v>
+        <v>600437</v>
       </c>
       <c r="AB211" t="n">
         <v>5</v>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -30340,7 +30340,7 @@
         <v>0</v>
       </c>
       <c r="O214" t="n">
-        <v>122365035.28</v>
+        <v>126289723.58</v>
       </c>
       <c r="P214" t="n">
         <v>49808521.04</v>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -30784,7 +30784,7 @@
         <v>0</v>
       </c>
       <c r="W217" t="n">
-        <v>141616875</v>
+        <v>136889022</v>
       </c>
       <c r="X217" t="n">
         <v>141616875</v>
@@ -30793,10 +30793,10 @@
         <v>4727853</v>
       </c>
       <c r="Z217" t="n">
-        <v>0</v>
+        <v>4727853</v>
       </c>
       <c r="AA217" t="n">
-        <v>141616875</v>
+        <v>136889022</v>
       </c>
       <c r="AB217" t="n">
         <v>5</v>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -30891,7 +30891,7 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>54651982.83</v>
+        <v>54741982.83</v>
       </c>
       <c r="M218" t="n">
         <v>0</v>
@@ -30900,7 +30900,7 @@
         <v>0</v>
       </c>
       <c r="O218" t="n">
-        <v>53892619.8</v>
+        <v>54317773.95</v>
       </c>
       <c r="P218" t="n">
         <v>50438263.91</v>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -31394,7 +31394,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -31534,7 +31534,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -31674,7 +31674,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>
@@ -31892,10 +31892,10 @@
         <v>48542457.07</v>
       </c>
       <c r="S225" t="n">
-        <v>38990514.67</v>
+        <v>39254641.52</v>
       </c>
       <c r="T225" t="n">
-        <v>40603278.83</v>
+        <v>40867405.68</v>
       </c>
       <c r="U225" t="n">
         <v>42154110.51</v>
@@ -31954,7 +31954,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>28/08/2026 18:00:38</t>
+          <t>29/08/2026 11:31:57</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202608.xlsx
+++ b/base_despesas/2026/despesas_202608.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -31394,7 +31394,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -31534,7 +31534,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -31674,7 +31674,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>
@@ -31954,7 +31954,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>29/08/2026 11:31:57</t>
+          <t>30/08/2026 11:36:02</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202608.xlsx
+++ b/base_despesas/2026/despesas_202608.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -31394,7 +31394,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -31534,7 +31534,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -31674,7 +31674,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
@@ -31954,7 +31954,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>30/08/2026 11:36:02</t>
+          <t>31/08/2026 14:09:10</t>
         </is>
       </c>
     </row>
